--- a/week-01/techsupply_dataset1.xlsx
+++ b/week-01/techsupply_dataset1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{74883D32-3818-4CB6-AD6A-C01298F817AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED436E4C-B857-4F81-B4A4-BD3F9A95F794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sales_Performance_Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="Calculations" sheetId="3" r:id="rId2"/>
+    <sheet name="Sales_Performance_Analysis" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sales_Data!$A$1:$K$301</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="176">
   <si>
     <t>Order_ID</t>
   </si>
@@ -528,10 +529,46 @@
     <t>3. Which region do they appear to sell in most often?</t>
   </si>
   <si>
-    <t xml:space="preserve">Furniture </t>
-  </si>
-  <si>
     <t>1. Which product category do business customers purchase most often?</t>
+  </si>
+  <si>
+    <t>Johnson and Brown</t>
+  </si>
+  <si>
+    <t>Brown and Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">East Region Analysis </t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Electronic</t>
+  </si>
+  <si>
+    <t>Most Frequent Sales Rep</t>
+  </si>
+  <si>
+    <t>Most Frequent Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Behavior Analysis </t>
+  </si>
+  <si>
+    <t>Payment Analysis</t>
+  </si>
+  <si>
+    <t>Most Frequent Product</t>
+  </si>
+  <si>
+    <t>Individual Transactions</t>
+  </si>
+  <si>
+    <t>Most Frequent Category (Business)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most Sold Product </t>
   </si>
 </sst>
 </file>
@@ -588,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -607,11 +644,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -625,6 +684,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{43FBAC21-8737-415F-8BA4-D0759F00F02F}" name="Table8" displayName="Table8" ref="A1:C13" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{B26E16DF-4AA3-47A8-A3B5-E25173132F28}" name="Task 1"/>
+    <tableColumn id="2" xr3:uid="{BAD8C39B-F492-4029-B8FD-2BF6003A6AFA}" name="East Region Analysis "/>
+    <tableColumn id="3" xr3:uid="{14D5A43A-2AD8-418E-A086-07F6639A83DF}" name="Count" dataDxfId="0">
+      <calculatedColumnFormula>COUNTIFS(Sales_Data!E1:E300, "Electronics", Sales_Data!C1:C300, "East")</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{92EFEFF6-E271-41B5-8D2F-C8CCB73D0EBA}" name="Table13456" displayName="Table13456" ref="D7:E11" totalsRowShown="0">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{850F673B-6FF0-4E3F-83CD-44B1D8883BDA}" name="Top Sales Representatives"/>
+    <tableColumn id="2" xr3:uid="{A00A7CFA-A286-45C1-9A47-EC191389B560}" name="Task 5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9E0352DF-5747-4B5C-B8BA-CED09577F1FC}" name="Table810" displayName="Table810" ref="A16:C28" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3C530DB1-E6C1-4E15-8518-F2A568C6725A}" name="Task 2"/>
+    <tableColumn id="2" xr3:uid="{A31607EF-477D-49CA-9965-8D62E698ECEA}" name="Customer Behavior Analysis "/>
+    <tableColumn id="3" xr3:uid="{46D3972F-5EA8-4134-BEC0-6C0029D4E972}" name="Count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{2AE02FFE-A29C-46DE-93B8-DF35334BDD50}" name="Table811" displayName="Table811" ref="A31:C44" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F16B666D-7FD7-45B0-8751-F243D221B5D2}" name="Task 3"/>
+    <tableColumn id="2" xr3:uid="{5412B964-EFD5-4299-9C37-340C993AE065}" name="Product Performance"/>
+    <tableColumn id="3" xr3:uid="{133C88DC-309E-46AE-8EBE-570BFA5D6202}" name="Count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCC4EAEC-96C3-4297-AFED-146BFBE50FC1}" name="Table812" displayName="Table812" ref="E1:G13" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D36FA3EA-AB79-4649-9BDA-6BD1C91C97AE}" name="Task 4"/>
+    <tableColumn id="2" xr3:uid="{6D4468A9-8D07-45E6-8DC2-FC2A69C44717}" name="Payment Analysis"/>
+    <tableColumn id="3" xr3:uid="{19DD1725-417A-427C-A4FA-7EC5E41A3336}" name="Count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9D5A2EF0-A8DD-4782-B852-D591D07EEE9D}" name="Table813" displayName="Table813" ref="E16:G28" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3AB681B7-2FF3-489D-ADCE-36216AC01947}" name="Task 5"/>
+    <tableColumn id="2" xr3:uid="{EBC1BC6D-77EB-4ECA-AB6B-AB6C517E5814}" name="Top Sales Representatives"/>
+    <tableColumn id="3" xr3:uid="{6B011237-243E-49AB-9F23-274A1F3983BE}" name="Count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3F3C98A2-6868-4EBE-A7C5-B07317085E5B}" name="Table1" displayName="Table1" ref="A1:B5" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8B5D81C5-19C3-4E39-89F4-1EB85C0703DD}" name="Regional Performance Analysis"/>
@@ -634,7 +760,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00C8E9C8-612C-42AA-9DF0-46F33BFE65BD}" name="Table13" displayName="Table13" ref="A7:B11" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4F222A82-E0FF-426C-AB90-4C8BE886D1DB}" name="Customer Behavior Analysis"/>
@@ -644,7 +770,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2954E9C1-5CCE-4A2E-99B0-2D1C3AA9D4B2}" name="Table134" displayName="Table134" ref="A13:B17" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{2476C571-C571-4885-92FA-8AFBE387CFF3}" name="Product Performance"/>
@@ -654,21 +780,11 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6A28EFAE-6E89-433C-B994-6B497F3B28EA}" name="Table1345" displayName="Table1345" ref="D1:E5" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{68A29675-25EA-441F-B53E-B39188716099}" name="Payment Pattern Analysis"/>
     <tableColumn id="2" xr3:uid="{24C3A92A-1222-473A-BDA2-61C868C69D25}" name="Task 4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{92EFEFF6-E271-41B5-8D2F-C8CCB73D0EBA}" name="Table13456" displayName="Table13456" ref="D7:E11" totalsRowShown="0">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{850F673B-6FF0-4E3F-83CD-44B1D8883BDA}" name="Top Sales Representatives"/>
-    <tableColumn id="2" xr3:uid="{A00A7CFA-A286-45C1-9A47-EC191389B560}" name="Task 5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -959,8 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K314"/>
+  <dimension ref="A1:K301"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10.59765625" customWidth="1"/>
@@ -1078,77 +1193,77 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2077</v>
+        <v>2208</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G4">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H4">
-        <v>312.29000000000002</v>
+        <v>722.55</v>
       </c>
       <c r="I4">
-        <v>20298.849999999999</v>
+        <v>44797.88</v>
       </c>
       <c r="J4" t="s">
         <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>2027</v>
+        <v>2198</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G5">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H5">
-        <v>947.36</v>
+        <v>875.17</v>
       </c>
       <c r="I5">
-        <v>34104.97</v>
+        <v>22754.45</v>
       </c>
       <c r="J5" t="s">
         <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2134</v>
       </c>
@@ -1183,15 +1298,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1203,19 +1318,19 @@
         <v>37</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="H7">
-        <v>306.77</v>
+        <v>312.29000000000002</v>
       </c>
       <c r="I7">
-        <v>8896.2800000000007</v>
+        <v>20298.849999999999</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
@@ -1253,7 +1368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2229</v>
       </c>
@@ -1288,7 +1403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2001</v>
       </c>
@@ -1323,7 +1438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2109</v>
       </c>
@@ -1358,7 +1473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2003</v>
       </c>
@@ -1393,33 +1508,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>2294</v>
+        <v>2051</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H13">
-        <v>63.98</v>
+        <v>357.11</v>
       </c>
       <c r="I13">
-        <v>1151.6600000000001</v>
+        <v>16784.23</v>
       </c>
       <c r="J13" t="s">
         <v>30</v>
@@ -1428,7 +1543,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>2202</v>
       </c>
@@ -1463,15 +1578,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>2208</v>
+        <v>2007</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1480,57 +1595,57 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="G15">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H15">
-        <v>722.55</v>
+        <v>197.97</v>
       </c>
       <c r="I15">
-        <v>44797.88</v>
+        <v>13461.99</v>
       </c>
       <c r="J15" t="s">
         <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>2205</v>
+        <v>2032</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="G16">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H16">
-        <v>364.9</v>
+        <v>183.07</v>
       </c>
       <c r="I16">
-        <v>24448.28</v>
+        <v>13181.33</v>
       </c>
       <c r="J16" t="s">
         <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
@@ -1570,7 +1685,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2198</v>
+        <v>2111</v>
       </c>
       <c r="B18" t="s">
         <v>93</v>
@@ -1588,13 +1703,13 @@
         <v>76</v>
       </c>
       <c r="G18">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H18">
-        <v>875.17</v>
+        <v>848.98</v>
       </c>
       <c r="I18">
-        <v>22754.45</v>
+        <v>12734.75</v>
       </c>
       <c r="J18" t="s">
         <v>30</v>
@@ -1638,12 +1753,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2032</v>
+        <v>2247</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1655,36 +1770,36 @@
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G20">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H20">
-        <v>183.07</v>
+        <v>233.65</v>
       </c>
       <c r="I20">
-        <v>13181.33</v>
+        <v>11215.09</v>
       </c>
       <c r="J20" t="s">
         <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2168</v>
+        <v>2076</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
@@ -1693,22 +1808,22 @@
         <v>37</v>
       </c>
       <c r="G21">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H21">
-        <v>292.62</v>
+        <v>306.77</v>
       </c>
       <c r="I21">
-        <v>22531.61</v>
+        <v>8896.2800000000007</v>
       </c>
       <c r="J21" t="s">
         <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2073</v>
       </c>
@@ -1743,15 +1858,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2247</v>
+        <v>2293</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -1760,25 +1875,25 @@
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G23">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="H23">
-        <v>233.65</v>
+        <v>113.2</v>
       </c>
       <c r="I23">
-        <v>11215.09</v>
+        <v>8489.64</v>
       </c>
       <c r="J23" t="s">
         <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>2113</v>
       </c>
@@ -1813,12 +1928,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2293</v>
+        <v>2097</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
@@ -1830,30 +1945,30 @@
         <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G25">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="H25">
-        <v>113.2</v>
+        <v>227.49</v>
       </c>
       <c r="I25">
-        <v>8489.64</v>
+        <v>8417.0400000000009</v>
       </c>
       <c r="J25" t="s">
         <v>30</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>2097</v>
+        <v>2275</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
@@ -1865,30 +1980,30 @@
         <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G26">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H26">
-        <v>227.49</v>
+        <v>213.11</v>
       </c>
       <c r="I26">
-        <v>8417.0400000000009</v>
+        <v>7032.67</v>
       </c>
       <c r="J26" t="s">
         <v>30</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
@@ -1903,62 +2018,62 @@
         <v>22</v>
       </c>
       <c r="G27">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H27">
-        <v>213.11</v>
+        <v>214.09</v>
       </c>
       <c r="I27">
-        <v>7032.67</v>
+        <v>5138.2</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>2286</v>
+        <v>2241</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G28">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="H28">
-        <v>214.09</v>
+        <v>26.54</v>
       </c>
       <c r="I28">
-        <v>5138.2</v>
+        <v>2096.9699999999998</v>
       </c>
       <c r="J28" t="s">
         <v>30</v>
       </c>
       <c r="K28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>2031</v>
+        <v>2294</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
@@ -1967,19 +2082,19 @@
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H29">
-        <v>264.7</v>
+        <v>63.98</v>
       </c>
       <c r="I29">
-        <v>529.4</v>
+        <v>1151.6600000000001</v>
       </c>
       <c r="J29" t="s">
         <v>30</v>
@@ -1988,15 +2103,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>2088</v>
+        <v>2031</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -2011,80 +2126,80 @@
         <v>2</v>
       </c>
       <c r="H30">
-        <v>258.82</v>
+        <v>264.7</v>
       </c>
       <c r="I30">
-        <v>517.65</v>
+        <v>529.4</v>
       </c>
       <c r="J30" t="s">
         <v>30</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>2159</v>
+        <v>2088</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="G31">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>6.51</v>
+        <v>258.82</v>
       </c>
       <c r="I31">
-        <v>299.27999999999997</v>
+        <v>517.65</v>
       </c>
       <c r="J31" t="s">
         <v>30</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>2067</v>
+        <v>2159</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="G32">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="H32">
-        <v>266.49</v>
+        <v>6.51</v>
       </c>
       <c r="I32">
-        <v>18654.61</v>
+        <v>299.27999999999997</v>
       </c>
       <c r="J32" t="s">
         <v>30</v>
@@ -2093,15 +2208,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33">
-        <v>2219</v>
+        <v>2063</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
@@ -2113,30 +2228,30 @@
         <v>65</v>
       </c>
       <c r="G33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H33">
-        <v>2.73</v>
+        <v>3.12</v>
       </c>
       <c r="I33">
-        <v>196.75</v>
+        <v>234.36</v>
       </c>
       <c r="J33" t="s">
         <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34">
-        <v>2121</v>
+        <v>2219</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
@@ -2145,16 +2260,16 @@
         <v>44</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G34">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="H34">
-        <v>5.94</v>
+        <v>2.73</v>
       </c>
       <c r="I34">
-        <v>184.1</v>
+        <v>196.75</v>
       </c>
       <c r="J34" t="s">
         <v>30</v>
@@ -2163,7 +2278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>2206</v>
       </c>
@@ -2198,7 +2313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2010</v>
       </c>
@@ -2233,12 +2348,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
@@ -2250,25 +2365,25 @@
         <v>44</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G37">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H37">
-        <v>3.82</v>
+        <v>5.94</v>
       </c>
       <c r="I37">
-        <v>145.32</v>
+        <v>184.1</v>
       </c>
       <c r="J37" t="s">
         <v>30</v>
       </c>
       <c r="K37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>2069</v>
       </c>
@@ -2303,7 +2418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>2095</v>
       </c>
@@ -2338,7 +2453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>2222</v>
       </c>
@@ -2443,7 +2558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>2037</v>
       </c>
@@ -2478,7 +2593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>2161</v>
       </c>
@@ -2515,40 +2630,40 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45">
-        <v>2051</v>
+        <v>2115</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G45">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H45">
-        <v>357.11</v>
+        <v>3.82</v>
       </c>
       <c r="I45">
-        <v>16784.23</v>
+        <v>145.32</v>
       </c>
       <c r="J45" t="s">
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>2155</v>
       </c>
@@ -2585,45 +2700,45 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47">
-        <v>2120</v>
+        <v>2128</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F47" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G47">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H47">
-        <v>819.18</v>
+        <v>1.52</v>
       </c>
       <c r="I47">
-        <v>13926.03</v>
+        <v>107.92</v>
       </c>
       <c r="J47" t="s">
         <v>30</v>
       </c>
       <c r="K47" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48">
-        <v>2007</v>
+        <v>2245</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -2632,25 +2747,25 @@
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G48">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="H48">
-        <v>197.97</v>
+        <v>2.98</v>
       </c>
       <c r="I48">
-        <v>13461.99</v>
+        <v>86.44</v>
       </c>
       <c r="J48" t="s">
         <v>30</v>
       </c>
       <c r="K48" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
@@ -2688,42 +2803,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50">
-        <v>2264</v>
+        <v>2136</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G50">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H50">
-        <v>25.78</v>
+        <v>1.58</v>
       </c>
       <c r="I50">
-        <v>1263.08</v>
+        <v>33.159999999999997</v>
       </c>
       <c r="J50" t="s">
         <v>30</v>
       </c>
       <c r="K50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>2017</v>
       </c>
@@ -2758,7 +2873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>2080</v>
       </c>
@@ -2793,7 +2908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>2006</v>
       </c>
@@ -2828,12 +2943,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54">
-        <v>2135</v>
+        <v>2036</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -2842,19 +2957,19 @@
         <v>36</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="H54">
-        <v>74.73</v>
+        <v>777.51</v>
       </c>
       <c r="I54">
-        <v>448.4</v>
+        <v>48982.99</v>
       </c>
       <c r="J54" t="s">
         <v>30</v>
@@ -2863,7 +2978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>2014</v>
       </c>
@@ -2898,33 +3013,33 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56">
-        <v>2099</v>
+        <v>2207</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
         <v>36</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F56" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="G56">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H56">
-        <v>20.84</v>
+        <v>738.51</v>
       </c>
       <c r="I56">
-        <v>333.42</v>
+        <v>13293.18</v>
       </c>
       <c r="J56" t="s">
         <v>30</v>
@@ -2968,42 +3083,42 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58">
-        <v>2036</v>
+        <v>2060</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D58" t="s">
         <v>36</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G58">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="H58">
-        <v>777.51</v>
+        <v>917.18</v>
       </c>
       <c r="I58">
-        <v>48982.99</v>
+        <v>12840.56</v>
       </c>
       <c r="J58" t="s">
         <v>30</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>2175</v>
       </c>
@@ -3038,103 +3153,103 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60">
-        <v>2207</v>
+        <v>2193</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s">
         <v>36</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F60" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G60">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="H60">
-        <v>738.51</v>
+        <v>163.9</v>
       </c>
       <c r="I60">
-        <v>13293.18</v>
+        <v>10817.59</v>
       </c>
       <c r="J60" t="s">
         <v>30</v>
       </c>
       <c r="K60" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61">
-        <v>2060</v>
+        <v>2236</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D61" t="s">
         <v>36</v>
       </c>
       <c r="E61" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="G61">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="H61">
-        <v>917.18</v>
+        <v>118.35</v>
       </c>
       <c r="I61">
-        <v>12840.56</v>
+        <v>7337.63</v>
       </c>
       <c r="J61" t="s">
         <v>30</v>
       </c>
       <c r="K61" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62">
-        <v>2111</v>
+        <v>2068</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E62" t="s">
         <v>21</v>
       </c>
       <c r="F62" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="G62">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="H62">
-        <v>848.98</v>
+        <v>115.14</v>
       </c>
       <c r="I62">
-        <v>12734.75</v>
+        <v>7023.42</v>
       </c>
       <c r="J62" t="s">
         <v>30</v>
@@ -3143,15 +3258,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63">
-        <v>2236</v>
+        <v>2043</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D63" t="s">
         <v>36</v>
@@ -3160,33 +3275,33 @@
         <v>21</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G63">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="H63">
-        <v>118.35</v>
+        <v>237.9</v>
       </c>
       <c r="I63">
-        <v>7337.63</v>
+        <v>4520.1000000000004</v>
       </c>
       <c r="J63" t="s">
         <v>30</v>
       </c>
       <c r="K63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D64" t="s">
         <v>36</v>
@@ -3198,19 +3313,19 @@
         <v>34</v>
       </c>
       <c r="G64">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="H64">
-        <v>115.14</v>
+        <v>114.84</v>
       </c>
       <c r="I64">
-        <v>7023.42</v>
+        <v>4249.08</v>
       </c>
       <c r="J64" t="s">
         <v>30</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
@@ -3248,7 +3363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>2133</v>
       </c>
@@ -3318,33 +3433,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68">
-        <v>2078</v>
+        <v>2050</v>
       </c>
       <c r="B68" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D68" t="s">
         <v>36</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="G68">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="H68">
-        <v>114.84</v>
+        <v>65.77</v>
       </c>
       <c r="I68">
-        <v>4249.08</v>
+        <v>3880.28</v>
       </c>
       <c r="J68" t="s">
         <v>30</v>
@@ -3355,10 +3470,10 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69">
-        <v>2193</v>
+        <v>2054</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
@@ -3367,19 +3482,19 @@
         <v>36</v>
       </c>
       <c r="E69" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69">
         <v>14</v>
       </c>
-      <c r="F69" t="s">
-        <v>82</v>
-      </c>
-      <c r="G69">
-        <v>66</v>
-      </c>
       <c r="H69">
-        <v>163.9</v>
+        <v>273.60000000000002</v>
       </c>
       <c r="I69">
-        <v>10817.59</v>
+        <v>3830.35</v>
       </c>
       <c r="J69" t="s">
         <v>30</v>
@@ -3388,7 +3503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>2197</v>
       </c>
@@ -3423,7 +3538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>2149</v>
       </c>
@@ -3460,48 +3575,48 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72">
-        <v>2235</v>
+        <v>2264</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="C72" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E72" t="s">
         <v>14</v>
       </c>
       <c r="F72" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="G72">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H72">
-        <v>188.4</v>
+        <v>25.78</v>
       </c>
       <c r="I72">
-        <v>10361.99</v>
+        <v>1263.08</v>
       </c>
       <c r="J72" t="s">
         <v>30</v>
       </c>
       <c r="K72" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73">
-        <v>2246</v>
+        <v>2239</v>
       </c>
       <c r="B73" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D73" t="s">
         <v>36</v>
@@ -3510,86 +3625,86 @@
         <v>44</v>
       </c>
       <c r="F73" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G73">
+        <v>79</v>
+      </c>
+      <c r="H73">
+        <v>5.95</v>
+      </c>
+      <c r="I73">
+        <v>470.22</v>
+      </c>
+      <c r="J73" t="s">
+        <v>30</v>
+      </c>
+      <c r="K73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>2135</v>
+      </c>
+      <c r="B74" t="s">
         <v>80</v>
       </c>
-      <c r="H73">
-        <v>4.07</v>
-      </c>
-      <c r="I73">
-        <v>325.64</v>
-      </c>
-      <c r="J73" t="s">
-        <v>30</v>
-      </c>
-      <c r="K73" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A74">
-        <v>2279</v>
-      </c>
-      <c r="B74" t="s">
-        <v>41</v>
-      </c>
       <c r="C74" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D74" t="s">
         <v>36</v>
       </c>
       <c r="E74" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="G74">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="H74">
-        <v>3.85</v>
+        <v>74.73</v>
       </c>
       <c r="I74">
-        <v>292.63</v>
+        <v>448.4</v>
       </c>
       <c r="J74" t="s">
         <v>30</v>
       </c>
       <c r="K74" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="G75">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H75">
-        <v>344.11</v>
+        <v>20.84</v>
       </c>
       <c r="I75">
-        <v>10323.200000000001</v>
+        <v>333.42</v>
       </c>
       <c r="J75" t="s">
         <v>30</v>
@@ -3598,7 +3713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>2124</v>
       </c>
@@ -3633,15 +3748,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77">
-        <v>2227</v>
+        <v>2246</v>
       </c>
       <c r="B77" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D77" t="s">
         <v>36</v>
@@ -3650,65 +3765,65 @@
         <v>44</v>
       </c>
       <c r="F77" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="G77">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="H77">
-        <v>6.3</v>
+        <v>4.07</v>
       </c>
       <c r="I77">
-        <v>214.07</v>
+        <v>325.64</v>
       </c>
       <c r="J77" t="s">
         <v>30</v>
       </c>
       <c r="K77" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78">
-        <v>2257</v>
+        <v>2040</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D78" t="s">
         <v>36</v>
       </c>
       <c r="E78" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G78">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="H78">
-        <v>2.92</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="I78">
-        <v>175.47</v>
+        <v>311.97000000000003</v>
       </c>
       <c r="J78" t="s">
         <v>30</v>
       </c>
       <c r="K78" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79">
-        <v>2147</v>
+        <v>2279</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -3723,22 +3838,22 @@
         <v>48</v>
       </c>
       <c r="G79">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H79">
-        <v>4.09</v>
+        <v>3.85</v>
       </c>
       <c r="I79">
-        <v>171.66</v>
+        <v>292.63</v>
       </c>
       <c r="J79" t="s">
         <v>30</v>
       </c>
       <c r="K79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>2274</v>
       </c>
@@ -3773,7 +3888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>2064</v>
       </c>
@@ -3808,7 +3923,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>2118</v>
       </c>
@@ -3843,74 +3958,74 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83">
-        <v>2282</v>
+        <v>2066</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F83" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G83">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="H83">
-        <v>929.75</v>
+        <v>3.79</v>
       </c>
       <c r="I83">
-        <v>32541.21</v>
+        <v>242.75</v>
       </c>
       <c r="J83" t="s">
         <v>30</v>
       </c>
       <c r="K83" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84">
-        <v>2045</v>
+        <v>2227</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F84" t="s">
+        <v>74</v>
+      </c>
+      <c r="G84">
         <v>34</v>
       </c>
-      <c r="G84">
-        <v>60</v>
-      </c>
       <c r="H84">
-        <v>131.07</v>
+        <v>6.3</v>
       </c>
       <c r="I84">
-        <v>7864.33</v>
+        <v>214.07</v>
       </c>
       <c r="J84" t="s">
         <v>30</v>
       </c>
       <c r="K84" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.45">
@@ -3948,77 +4063,77 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="B86" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F86" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G86">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H86">
-        <v>23.17</v>
+        <v>2.92</v>
       </c>
       <c r="I86">
-        <v>1806.92</v>
+        <v>175.47</v>
       </c>
       <c r="J86" t="s">
         <v>30</v>
       </c>
       <c r="K86" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87">
-        <v>2223</v>
+        <v>2147</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F87" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G87">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="H87">
-        <v>20.11</v>
+        <v>4.09</v>
       </c>
       <c r="I87">
-        <v>1045.76</v>
+        <v>171.66</v>
       </c>
       <c r="J87" t="s">
         <v>30</v>
       </c>
       <c r="K87" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>2261</v>
       </c>
@@ -4088,7 +4203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>2199</v>
       </c>
@@ -4123,7 +4238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>2122</v>
       </c>
@@ -4193,7 +4308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>2176</v>
       </c>
@@ -4228,7 +4343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>2075</v>
       </c>
@@ -4298,33 +4413,33 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96">
-        <v>2042</v>
+        <v>2282</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D96" t="s">
         <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="G96">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="H96">
-        <v>219.16</v>
+        <v>929.75</v>
       </c>
       <c r="I96">
-        <v>16437.080000000002</v>
+        <v>32541.21</v>
       </c>
       <c r="J96" t="s">
         <v>30</v>
@@ -4333,7 +4448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>2125</v>
       </c>
@@ -4368,15 +4483,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98">
-        <v>2268</v>
+        <v>2205</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C98" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D98" t="s">
         <v>33</v>
@@ -4385,16 +4500,16 @@
         <v>21</v>
       </c>
       <c r="F98" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G98">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H98">
-        <v>258.70999999999998</v>
+        <v>364.9</v>
       </c>
       <c r="I98">
-        <v>15263.72</v>
+        <v>24448.28</v>
       </c>
       <c r="J98" t="s">
         <v>30</v>
@@ -4403,12 +4518,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99">
-        <v>2217</v>
+        <v>2042</v>
       </c>
       <c r="B99" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C99" t="s">
         <v>27</v>
@@ -4423,13 +4538,13 @@
         <v>22</v>
       </c>
       <c r="G99">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H99">
-        <v>211.93</v>
+        <v>219.16</v>
       </c>
       <c r="I99">
-        <v>11655.94</v>
+        <v>16437.080000000002</v>
       </c>
       <c r="J99" t="s">
         <v>30</v>
@@ -4438,7 +4553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>2072</v>
       </c>
@@ -4473,15 +4588,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101">
-        <v>2284</v>
+        <v>2268</v>
       </c>
       <c r="B101" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D101" t="s">
         <v>33</v>
@@ -4493,19 +4608,19 @@
         <v>42</v>
       </c>
       <c r="G101">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="H101">
-        <v>237.4</v>
+        <v>258.70999999999998</v>
       </c>
       <c r="I101">
-        <v>9970.85</v>
+        <v>15263.72</v>
       </c>
       <c r="J101" t="s">
         <v>30</v>
       </c>
       <c r="K101" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.45">
@@ -4580,48 +4695,48 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A104">
-        <v>2232</v>
+        <v>2217</v>
       </c>
       <c r="B104" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="C104" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E104" t="s">
         <v>21</v>
       </c>
       <c r="F104" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="G104">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="H104">
-        <v>352.03</v>
+        <v>211.93</v>
       </c>
       <c r="I104">
-        <v>4576.33</v>
+        <v>11655.94</v>
       </c>
       <c r="J104" t="s">
         <v>30</v>
       </c>
       <c r="K104" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A105">
-        <v>2234</v>
+        <v>2284</v>
       </c>
       <c r="B105" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C105" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D105" t="s">
         <v>33</v>
@@ -4630,68 +4745,68 @@
         <v>21</v>
       </c>
       <c r="F105" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G105">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H105">
-        <v>216.99</v>
+        <v>237.4</v>
       </c>
       <c r="I105">
-        <v>4556.6899999999996</v>
+        <v>9970.85</v>
       </c>
       <c r="J105" t="s">
         <v>30</v>
       </c>
       <c r="K105" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A106">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="C106" t="s">
         <v>32</v>
       </c>
       <c r="D106" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E106" t="s">
         <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G106">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="H106">
-        <v>237.9</v>
+        <v>131.07</v>
       </c>
       <c r="I106">
-        <v>4520.1000000000004</v>
+        <v>7864.33</v>
       </c>
       <c r="J106" t="s">
         <v>30</v>
       </c>
       <c r="K106" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A107">
-        <v>2164</v>
+        <v>2234</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D107" t="s">
         <v>33</v>
@@ -4700,16 +4815,16 @@
         <v>21</v>
       </c>
       <c r="F107" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G107">
         <v>21</v>
       </c>
       <c r="H107">
-        <v>116.49</v>
+        <v>216.99</v>
       </c>
       <c r="I107">
-        <v>2446.35</v>
+        <v>4556.6899999999996</v>
       </c>
       <c r="J107" t="s">
         <v>30</v>
@@ -4753,33 +4868,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A109">
-        <v>2251</v>
+        <v>2164</v>
       </c>
       <c r="B109" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="C109" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D109" t="s">
         <v>33</v>
       </c>
       <c r="E109" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F109" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="G109">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H109">
-        <v>5.85</v>
+        <v>116.49</v>
       </c>
       <c r="I109">
-        <v>380.26</v>
+        <v>2446.35</v>
       </c>
       <c r="J109" t="s">
         <v>30</v>
@@ -4823,7 +4938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>2276</v>
       </c>
@@ -4858,7 +4973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>2210</v>
       </c>
@@ -4893,33 +5008,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A113">
-        <v>2038</v>
+        <v>2262</v>
       </c>
       <c r="B113" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C113" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D113" t="s">
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F113" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G113">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H113">
-        <v>2.93</v>
+        <v>23.17</v>
       </c>
       <c r="I113">
-        <v>193.45</v>
+        <v>1806.92</v>
       </c>
       <c r="J113" t="s">
         <v>30</v>
@@ -4928,68 +5043,68 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A114">
-        <v>2090</v>
+        <v>2223</v>
       </c>
       <c r="B114" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D114" t="s">
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F114" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G114">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="H114">
-        <v>6.1</v>
+        <v>20.11</v>
       </c>
       <c r="I114">
-        <v>177.04</v>
+        <v>1045.76</v>
       </c>
       <c r="J114" t="s">
         <v>30</v>
       </c>
       <c r="K114" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A115">
-        <v>2204</v>
+        <v>2093</v>
       </c>
       <c r="B115" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D115" t="s">
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G115">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H115">
-        <v>2.94</v>
+        <v>22.72</v>
       </c>
       <c r="I115">
-        <v>152.9</v>
+        <v>977.16</v>
       </c>
       <c r="J115" t="s">
         <v>30</v>
@@ -4998,15 +5113,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A116">
-        <v>2126</v>
+        <v>2251</v>
       </c>
       <c r="B116" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D116" t="s">
         <v>33</v>
@@ -5015,16 +5130,16 @@
         <v>44</v>
       </c>
       <c r="F116" t="s">
+        <v>74</v>
+      </c>
+      <c r="G116">
         <v>65</v>
       </c>
-      <c r="G116">
-        <v>39</v>
-      </c>
       <c r="H116">
-        <v>2.8</v>
+        <v>5.85</v>
       </c>
       <c r="I116">
-        <v>109.11</v>
+        <v>380.26</v>
       </c>
       <c r="J116" t="s">
         <v>30</v>
@@ -5033,7 +5148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>2233</v>
       </c>
@@ -5068,15 +5183,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A118">
-        <v>2299</v>
+        <v>2047</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D118" t="s">
         <v>33</v>
@@ -5085,33 +5200,33 @@
         <v>44</v>
       </c>
       <c r="F118" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G118">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H118">
-        <v>1.56</v>
+        <v>3.87</v>
       </c>
       <c r="I118">
-        <v>94.9</v>
+        <v>255.19</v>
       </c>
       <c r="J118" t="s">
         <v>30</v>
       </c>
       <c r="K118" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A119">
-        <v>2195</v>
+        <v>2038</v>
       </c>
       <c r="B119" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C119" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D119" t="s">
         <v>33</v>
@@ -5120,33 +5235,33 @@
         <v>44</v>
       </c>
       <c r="F119" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G119">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H119">
-        <v>6.17</v>
+        <v>2.93</v>
       </c>
       <c r="I119">
-        <v>80.239999999999995</v>
+        <v>193.45</v>
       </c>
       <c r="J119" t="s">
         <v>30</v>
       </c>
       <c r="K119" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A120">
-        <v>2250</v>
+        <v>2090</v>
       </c>
       <c r="B120" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C120" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D120" t="s">
         <v>33</v>
@@ -5158,19 +5273,19 @@
         <v>74</v>
       </c>
       <c r="G120">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H120">
-        <v>5.99</v>
+        <v>6.1</v>
       </c>
       <c r="I120">
-        <v>53.93</v>
+        <v>177.04</v>
       </c>
       <c r="J120" t="s">
         <v>30</v>
       </c>
       <c r="K120" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.45">
@@ -5208,15 +5323,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A122">
-        <v>2170</v>
+        <v>2204</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="C122" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D122" t="s">
         <v>33</v>
@@ -5225,127 +5340,127 @@
         <v>44</v>
       </c>
       <c r="F122" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G122">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="H122">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="I122">
-        <v>21.71</v>
+        <v>152.9</v>
       </c>
       <c r="J122" t="s">
         <v>30</v>
       </c>
       <c r="K122" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A123">
-        <v>2050</v>
+        <v>2056</v>
       </c>
       <c r="B123" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C123" t="s">
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E123" t="s">
         <v>14</v>
       </c>
       <c r="F123" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="G123">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="H123">
-        <v>65.77</v>
+        <v>18.12</v>
       </c>
       <c r="I123">
-        <v>3880.28</v>
+        <v>144.97999999999999</v>
       </c>
       <c r="J123" t="s">
         <v>30</v>
       </c>
       <c r="K123" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A124">
-        <v>2071</v>
+        <v>2126</v>
       </c>
       <c r="B124" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D124" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F124" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G124">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="H124">
-        <v>59.14</v>
+        <v>2.8</v>
       </c>
       <c r="I124">
-        <v>3843.89</v>
+        <v>109.11</v>
       </c>
       <c r="J124" t="s">
         <v>30</v>
       </c>
       <c r="K124" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A125">
-        <v>2054</v>
+        <v>2299</v>
       </c>
       <c r="B125" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C125" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D125" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F125" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G125">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="H125">
-        <v>273.60000000000002</v>
+        <v>1.56</v>
       </c>
       <c r="I125">
-        <v>3830.35</v>
+        <v>94.9</v>
       </c>
       <c r="J125" t="s">
         <v>30</v>
       </c>
       <c r="K125" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.45">
@@ -5418,39 +5533,39 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A128">
-        <v>2213</v>
+        <v>2195</v>
       </c>
       <c r="B128" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C128" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D128" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E128" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F128" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="G128">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="H128">
-        <v>18.190000000000001</v>
+        <v>6.17</v>
       </c>
       <c r="I128">
-        <v>854.76</v>
+        <v>80.239999999999995</v>
       </c>
       <c r="J128" t="s">
         <v>30</v>
       </c>
       <c r="K128" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.45">
@@ -5488,7 +5603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>2187</v>
       </c>
@@ -5523,7 +5638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>2291</v>
       </c>
@@ -5558,7 +5673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>2171</v>
       </c>
@@ -5593,7 +5708,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>2265</v>
       </c>
@@ -5630,40 +5745,40 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A134">
-        <v>2241</v>
+        <v>2250</v>
       </c>
       <c r="B134" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C134" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D134" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E134" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F134" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G134">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="H134">
-        <v>26.54</v>
+        <v>5.99</v>
       </c>
       <c r="I134">
-        <v>2096.9699999999998</v>
+        <v>53.93</v>
       </c>
       <c r="J134" t="s">
         <v>30</v>
       </c>
       <c r="K134" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>2094</v>
       </c>
@@ -5698,7 +5813,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>2030</v>
       </c>
@@ -5733,7 +5848,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>2289</v>
       </c>
@@ -5768,33 +5883,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A138">
-        <v>2252</v>
+        <v>2025</v>
       </c>
       <c r="B138" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="C138" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D138" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F138" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G138">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H138">
-        <v>247.68</v>
+        <v>3.15</v>
       </c>
       <c r="I138">
-        <v>8916.49</v>
+        <v>37.76</v>
       </c>
       <c r="J138" t="s">
         <v>30</v>
@@ -5803,33 +5918,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A139">
-        <v>2152</v>
+        <v>2170</v>
       </c>
       <c r="B139" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D139" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E139" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F139" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G139">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H139">
-        <v>127.61</v>
+        <v>1.55</v>
       </c>
       <c r="I139">
-        <v>2041.78</v>
+        <v>21.71</v>
       </c>
       <c r="J139" t="s">
         <v>30</v>
@@ -5875,31 +5990,31 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A141">
-        <v>2108</v>
+        <v>2027</v>
       </c>
       <c r="B141" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C141" t="s">
         <v>32</v>
       </c>
       <c r="D141" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E141" t="s">
         <v>14</v>
       </c>
       <c r="F141" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G141">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H141">
-        <v>63.22</v>
+        <v>947.36</v>
       </c>
       <c r="I141">
-        <v>1643.82</v>
+        <v>34104.97</v>
       </c>
       <c r="J141" t="s">
         <v>30</v>
@@ -5908,68 +6023,68 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A142">
-        <v>2057</v>
+        <v>2168</v>
       </c>
       <c r="B142" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D142" t="s">
         <v>47</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F142" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G142">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H142">
-        <v>8.02</v>
+        <v>292.62</v>
       </c>
       <c r="I142">
-        <v>625.57000000000005</v>
+        <v>22531.61</v>
       </c>
       <c r="J142" t="s">
         <v>30</v>
       </c>
       <c r="K142" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A143">
-        <v>2154</v>
+        <v>2120</v>
       </c>
       <c r="B143" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="C143" t="s">
         <v>32</v>
       </c>
       <c r="D143" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E143" t="s">
         <v>14</v>
       </c>
       <c r="F143" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G143">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="H143">
-        <v>27.2</v>
+        <v>819.18</v>
       </c>
       <c r="I143">
-        <v>1605.07</v>
+        <v>13926.03</v>
       </c>
       <c r="J143" t="s">
         <v>30</v>
@@ -6013,47 +6128,47 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A145">
-        <v>2179</v>
+        <v>2100</v>
       </c>
       <c r="B145" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C145" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D145" t="s">
         <v>47</v>
       </c>
       <c r="E145" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F145" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G145">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="H145">
-        <v>2.71</v>
+        <v>344.11</v>
       </c>
       <c r="I145">
-        <v>197.81</v>
+        <v>10323.200000000001</v>
       </c>
       <c r="J145" t="s">
         <v>30</v>
       </c>
       <c r="K145" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A146">
-        <v>2181</v>
+        <v>2252</v>
       </c>
       <c r="B146" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C146" t="s">
         <v>19</v>
@@ -6062,98 +6177,98 @@
         <v>47</v>
       </c>
       <c r="E146" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G146">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H146">
-        <v>3.04</v>
+        <v>247.68</v>
       </c>
       <c r="I146">
-        <v>164.28</v>
+        <v>8916.49</v>
       </c>
       <c r="J146" t="s">
         <v>30</v>
       </c>
       <c r="K146" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A147">
-        <v>2243</v>
+        <v>2152</v>
       </c>
       <c r="B147" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D147" t="s">
         <v>47</v>
       </c>
       <c r="E147" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="G147">
+        <v>16</v>
+      </c>
+      <c r="H147">
+        <v>127.61</v>
+      </c>
+      <c r="I147">
+        <v>2041.78</v>
+      </c>
+      <c r="J147" t="s">
+        <v>30</v>
+      </c>
+      <c r="K147" t="s">
         <v>23</v>
       </c>
-      <c r="H147">
-        <v>60.07</v>
-      </c>
-      <c r="I147">
-        <v>1381.54</v>
-      </c>
-      <c r="J147" t="s">
-        <v>30</v>
-      </c>
-      <c r="K147" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A148">
-        <v>2218</v>
+        <v>2243</v>
       </c>
       <c r="B148" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D148" t="s">
         <v>47</v>
       </c>
       <c r="E148" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G148">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H148">
-        <v>3.14</v>
+        <v>60.07</v>
       </c>
       <c r="I148">
-        <v>81.63</v>
+        <v>1381.54</v>
       </c>
       <c r="J148" t="s">
         <v>30</v>
       </c>
       <c r="K148" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>2190</v>
       </c>
@@ -6188,7 +6303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>2084</v>
       </c>
@@ -6223,12 +6338,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A151">
-        <v>2058</v>
+        <v>2213</v>
       </c>
       <c r="B151" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C151" t="s">
         <v>27</v>
@@ -6237,19 +6352,19 @@
         <v>47</v>
       </c>
       <c r="E151" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F151" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G151">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H151">
-        <v>8.76</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="I151">
-        <v>70.069999999999993</v>
+        <v>854.76</v>
       </c>
       <c r="J151" t="s">
         <v>30</v>
@@ -6258,12 +6373,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A152">
-        <v>2259</v>
+        <v>2057</v>
       </c>
       <c r="B152" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="C152" t="s">
         <v>27</v>
@@ -6278,118 +6393,118 @@
         <v>45</v>
       </c>
       <c r="G152">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="H152">
-        <v>7.34</v>
+        <v>8.02</v>
       </c>
       <c r="I152">
-        <v>51.35</v>
+        <v>625.57000000000005</v>
       </c>
       <c r="J152" t="s">
         <v>30</v>
       </c>
       <c r="K152" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A153">
-        <v>2277</v>
+        <v>2216</v>
       </c>
       <c r="B153" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="C153" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D153" t="s">
         <v>47</v>
       </c>
       <c r="E153" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F153" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="G153">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H153">
-        <v>1.57</v>
+        <v>58.11</v>
       </c>
       <c r="I153">
-        <v>43.97</v>
+        <v>348.65</v>
       </c>
       <c r="J153" t="s">
         <v>30</v>
       </c>
       <c r="K153" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A154">
-        <v>2141</v>
+        <v>2179</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C154" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D154" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E154" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F154" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G154">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H154">
-        <v>20.62</v>
+        <v>2.71</v>
       </c>
       <c r="I154">
-        <v>1216.45</v>
+        <v>197.81</v>
       </c>
       <c r="J154" t="s">
         <v>30</v>
       </c>
       <c r="K154" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A155">
-        <v>2255</v>
+        <v>2181</v>
       </c>
       <c r="B155" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="C155" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D155" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E155" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F155" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G155">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H155">
-        <v>834.97</v>
+        <v>3.04</v>
       </c>
       <c r="I155">
-        <v>43418.32</v>
+        <v>164.28</v>
       </c>
       <c r="J155" t="s">
         <v>30</v>
@@ -6398,7 +6513,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>2191</v>
       </c>
@@ -6435,31 +6550,31 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A157">
-        <v>2160</v>
+        <v>2012</v>
       </c>
       <c r="B157" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C157" t="s">
         <v>32</v>
       </c>
       <c r="D157" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E157" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F157" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G157">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="H157">
-        <v>24.4</v>
+        <v>1.55</v>
       </c>
       <c r="I157">
-        <v>1171.1099999999999</v>
+        <v>113.04</v>
       </c>
       <c r="J157" t="s">
         <v>30</v>
@@ -6468,7 +6583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>2254</v>
       </c>
@@ -6503,7 +6618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>2008</v>
       </c>
@@ -6540,66 +6655,66 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A160">
-        <v>2143</v>
+        <v>2218</v>
       </c>
       <c r="B160" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="C160" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E160" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F160" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G160">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H160">
-        <v>58.05</v>
+        <v>3.14</v>
       </c>
       <c r="I160">
-        <v>1044.9000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="J160" t="s">
         <v>30</v>
       </c>
       <c r="K160" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A161">
-        <v>2093</v>
+        <v>2058</v>
       </c>
       <c r="B161" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C161" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D161" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E161" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F161" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G161">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H161">
-        <v>22.72</v>
+        <v>8.76</v>
       </c>
       <c r="I161">
-        <v>977.16</v>
+        <v>70.069999999999993</v>
       </c>
       <c r="J161" t="s">
         <v>30</v>
@@ -6608,7 +6723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>2013</v>
       </c>
@@ -6643,68 +6758,68 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A163">
-        <v>2049</v>
+        <v>2259</v>
       </c>
       <c r="B163" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="C163" t="s">
         <v>27</v>
       </c>
       <c r="D163" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E163" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F163" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G163">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H163">
-        <v>317.58</v>
+        <v>7.34</v>
       </c>
       <c r="I163">
-        <v>3493.43</v>
+        <v>51.35</v>
       </c>
       <c r="J163" t="s">
         <v>30</v>
       </c>
       <c r="K163" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A164">
-        <v>2224</v>
+        <v>2277</v>
       </c>
       <c r="B164" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C164" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D164" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E164" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F164" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G164">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H164">
-        <v>869.36</v>
+        <v>1.57</v>
       </c>
       <c r="I164">
-        <v>869.36</v>
+        <v>43.97</v>
       </c>
       <c r="J164" t="s">
         <v>30</v>
@@ -6750,37 +6865,37 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A166">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="B166" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C166" t="s">
         <v>32</v>
       </c>
       <c r="D166" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E166" t="s">
         <v>44</v>
       </c>
       <c r="F166" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="G166">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="H166">
-        <v>5.95</v>
+        <v>3.93</v>
       </c>
       <c r="I166">
-        <v>470.22</v>
+        <v>31.45</v>
       </c>
       <c r="J166" t="s">
         <v>30</v>
       </c>
       <c r="K166" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.45">
@@ -6820,75 +6935,75 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A168">
-        <v>2163</v>
+        <v>2255</v>
       </c>
       <c r="B168" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="C168" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168" t="s">
+        <v>40</v>
+      </c>
+      <c r="E168" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168" t="s">
+        <v>68</v>
+      </c>
+      <c r="G168">
+        <v>52</v>
+      </c>
+      <c r="H168">
+        <v>834.97</v>
+      </c>
+      <c r="I168">
+        <v>43418.32</v>
+      </c>
+      <c r="J168" t="s">
+        <v>30</v>
+      </c>
+      <c r="K168" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A169">
+        <v>2067</v>
+      </c>
+      <c r="B169" t="s">
+        <v>96</v>
+      </c>
+      <c r="C169" t="s">
         <v>32</v>
-      </c>
-      <c r="D168" t="s">
-        <v>20</v>
-      </c>
-      <c r="E168" t="s">
-        <v>44</v>
-      </c>
-      <c r="F168" t="s">
-        <v>74</v>
-      </c>
-      <c r="G168">
-        <v>71</v>
-      </c>
-      <c r="H168">
-        <v>5.77</v>
-      </c>
-      <c r="I168">
-        <v>410.01</v>
-      </c>
-      <c r="J168" t="s">
-        <v>30</v>
-      </c>
-      <c r="K168" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A169">
-        <v>2105</v>
-      </c>
-      <c r="B169" t="s">
-        <v>99</v>
-      </c>
-      <c r="C169" t="s">
-        <v>27</v>
       </c>
       <c r="D169" t="s">
         <v>40</v>
       </c>
       <c r="E169" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F169" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G169">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="H169">
-        <v>72.819999999999993</v>
+        <v>266.49</v>
       </c>
       <c r="I169">
-        <v>145.63999999999999</v>
+        <v>18654.61</v>
       </c>
       <c r="J169" t="s">
         <v>30</v>
       </c>
       <c r="K169" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>2039</v>
       </c>
@@ -6923,7 +7038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>2156</v>
       </c>
@@ -6958,7 +7073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>2145</v>
       </c>
@@ -6993,7 +7108,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>2144</v>
       </c>
@@ -7028,7 +7143,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>2196</v>
       </c>
@@ -7065,66 +7180,66 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A175">
-        <v>2216</v>
+        <v>2297</v>
       </c>
       <c r="B175" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="C175" t="s">
+        <v>12</v>
+      </c>
+      <c r="D175" t="s">
+        <v>40</v>
+      </c>
+      <c r="E175" t="s">
+        <v>21</v>
+      </c>
+      <c r="F175" t="s">
+        <v>34</v>
+      </c>
+      <c r="G175">
+        <v>74</v>
+      </c>
+      <c r="H175">
+        <v>123.59</v>
+      </c>
+      <c r="I175">
+        <v>9146.02</v>
+      </c>
+      <c r="J175" t="s">
+        <v>30</v>
+      </c>
+      <c r="K175" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A176">
+        <v>2071</v>
+      </c>
+      <c r="B176" t="s">
+        <v>97</v>
+      </c>
+      <c r="C176" t="s">
         <v>32</v>
-      </c>
-      <c r="D175" t="s">
-        <v>47</v>
-      </c>
-      <c r="E175" t="s">
-        <v>14</v>
-      </c>
-      <c r="F175" t="s">
-        <v>87</v>
-      </c>
-      <c r="G175">
-        <v>6</v>
-      </c>
-      <c r="H175">
-        <v>58.11</v>
-      </c>
-      <c r="I175">
-        <v>348.65</v>
-      </c>
-      <c r="J175" t="s">
-        <v>30</v>
-      </c>
-      <c r="K175" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A176">
-        <v>2297</v>
-      </c>
-      <c r="B176" t="s">
-        <v>96</v>
-      </c>
-      <c r="C176" t="s">
-        <v>12</v>
       </c>
       <c r="D176" t="s">
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F176" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="G176">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H176">
-        <v>123.59</v>
+        <v>59.14</v>
       </c>
       <c r="I176">
-        <v>9146.02</v>
+        <v>3843.89</v>
       </c>
       <c r="J176" t="s">
         <v>30</v>
@@ -7133,33 +7248,33 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A177">
-        <v>2083</v>
+        <v>2049</v>
       </c>
       <c r="B177" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C177" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D177" t="s">
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F177" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G177">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H177">
-        <v>120.19</v>
+        <v>317.58</v>
       </c>
       <c r="I177">
-        <v>2283.56</v>
+        <v>3493.43</v>
       </c>
       <c r="J177" t="s">
         <v>30</v>
@@ -7168,15 +7283,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A178">
-        <v>2258</v>
+        <v>2083</v>
       </c>
       <c r="B178" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C178" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D178" t="s">
         <v>40</v>
@@ -7185,16 +7300,16 @@
         <v>21</v>
       </c>
       <c r="F178" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G178">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H178">
-        <v>207.19</v>
+        <v>120.19</v>
       </c>
       <c r="I178">
-        <v>1864.75</v>
+        <v>2283.56</v>
       </c>
       <c r="J178" t="s">
         <v>30</v>
@@ -7205,66 +7320,66 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A179">
-        <v>2040</v>
+        <v>2258</v>
       </c>
       <c r="B179" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C179" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179" t="s">
+        <v>40</v>
+      </c>
+      <c r="E179" t="s">
+        <v>21</v>
+      </c>
+      <c r="F179" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179">
+        <v>9</v>
+      </c>
+      <c r="H179">
+        <v>207.19</v>
+      </c>
+      <c r="I179">
+        <v>1864.75</v>
+      </c>
+      <c r="J179" t="s">
+        <v>30</v>
+      </c>
+      <c r="K179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A180">
+        <v>2108</v>
+      </c>
+      <c r="B180" t="s">
+        <v>92</v>
+      </c>
+      <c r="C180" t="s">
         <v>32</v>
-      </c>
-      <c r="D179" t="s">
-        <v>36</v>
-      </c>
-      <c r="E179" t="s">
-        <v>14</v>
-      </c>
-      <c r="F179" t="s">
-        <v>29</v>
-      </c>
-      <c r="G179">
-        <v>17</v>
-      </c>
-      <c r="H179">
-        <v>18.350000000000001</v>
-      </c>
-      <c r="I179">
-        <v>311.97000000000003</v>
-      </c>
-      <c r="J179" t="s">
-        <v>30</v>
-      </c>
-      <c r="K179" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A180">
-        <v>2221</v>
-      </c>
-      <c r="B180" t="s">
-        <v>84</v>
-      </c>
-      <c r="C180" t="s">
-        <v>27</v>
       </c>
       <c r="D180" t="s">
         <v>40</v>
       </c>
       <c r="E180" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F180" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="G180">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="H180">
-        <v>8.07</v>
+        <v>63.22</v>
       </c>
       <c r="I180">
-        <v>572.64</v>
+        <v>1643.82</v>
       </c>
       <c r="J180" t="s">
         <v>30</v>
@@ -7273,33 +7388,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A181">
-        <v>2104</v>
+        <v>2141</v>
       </c>
       <c r="B181" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C181" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D181" t="s">
         <v>40</v>
       </c>
       <c r="E181" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F181" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G181">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H181">
-        <v>7.3</v>
+        <v>20.62</v>
       </c>
       <c r="I181">
-        <v>386.92</v>
+        <v>1216.45</v>
       </c>
       <c r="J181" t="s">
         <v>30</v>
@@ -7308,7 +7423,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>2137</v>
       </c>
@@ -7343,7 +7458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>2167</v>
       </c>
@@ -7378,33 +7493,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A184">
-        <v>2029</v>
+        <v>2160</v>
       </c>
       <c r="B184" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C184" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D184" t="s">
         <v>40</v>
       </c>
       <c r="E184" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F184" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G184">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H184">
-        <v>7.21</v>
+        <v>24.4</v>
       </c>
       <c r="I184">
-        <v>310.10000000000002</v>
+        <v>1171.1099999999999</v>
       </c>
       <c r="J184" t="s">
         <v>30</v>
@@ -7413,39 +7528,39 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A185">
-        <v>2101</v>
+        <v>2143</v>
       </c>
       <c r="B185" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C185" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D185" t="s">
         <v>40</v>
       </c>
       <c r="E185" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F185" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G185">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H185">
-        <v>6.51</v>
+        <v>58.05</v>
       </c>
       <c r="I185">
-        <v>149.63</v>
+        <v>1044.9000000000001</v>
       </c>
       <c r="J185" t="s">
         <v>30</v>
       </c>
       <c r="K185" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.45">
@@ -7483,33 +7598,33 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A187">
-        <v>2278</v>
+        <v>2224</v>
       </c>
       <c r="B187" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C187" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D187" t="s">
         <v>40</v>
       </c>
       <c r="E187" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F187" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G187">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H187">
-        <v>4.24</v>
+        <v>869.36</v>
       </c>
       <c r="I187">
-        <v>135.71</v>
+        <v>869.36</v>
       </c>
       <c r="J187" t="s">
         <v>30</v>
@@ -7553,7 +7668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>2114</v>
       </c>
@@ -7588,7 +7703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>2146</v>
       </c>
@@ -7623,7 +7738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>2281</v>
       </c>
@@ -7658,12 +7773,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A192">
-        <v>2230</v>
+        <v>2221</v>
       </c>
       <c r="B192" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="C192" t="s">
         <v>27</v>
@@ -7675,25 +7790,25 @@
         <v>44</v>
       </c>
       <c r="F192" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G192">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="H192">
-        <v>3.61</v>
+        <v>8.07</v>
       </c>
       <c r="I192">
-        <v>3.61</v>
+        <v>572.64</v>
       </c>
       <c r="J192" t="s">
         <v>30</v>
       </c>
       <c r="K192" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>2065</v>
       </c>
@@ -7728,68 +7843,68 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A194">
-        <v>2185</v>
+        <v>2104</v>
       </c>
       <c r="B194" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C194" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D194" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E194" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F194" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="G194">
+        <v>53</v>
+      </c>
+      <c r="H194">
+        <v>7.3</v>
+      </c>
+      <c r="I194">
+        <v>386.92</v>
+      </c>
+      <c r="J194" t="s">
+        <v>30</v>
+      </c>
+      <c r="K194" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A195">
+        <v>2029</v>
+      </c>
+      <c r="B195" t="s">
+        <v>70</v>
+      </c>
+      <c r="C195" t="s">
+        <v>12</v>
+      </c>
+      <c r="D195" t="s">
+        <v>40</v>
+      </c>
+      <c r="E195" t="s">
         <v>44</v>
       </c>
-      <c r="H194">
-        <v>873.88</v>
-      </c>
-      <c r="I194">
-        <v>38450.699999999997</v>
-      </c>
-      <c r="J194" t="s">
-        <v>30</v>
-      </c>
-      <c r="K194" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A195">
-        <v>2138</v>
-      </c>
-      <c r="B195" t="s">
-        <v>92</v>
-      </c>
-      <c r="C195" t="s">
-        <v>19</v>
-      </c>
-      <c r="D195" t="s">
-        <v>20</v>
-      </c>
-      <c r="E195" t="s">
-        <v>14</v>
-      </c>
       <c r="F195" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G195">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="H195">
-        <v>295.58</v>
+        <v>7.21</v>
       </c>
       <c r="I195">
-        <v>22463.9</v>
+        <v>310.10000000000002</v>
       </c>
       <c r="J195" t="s">
         <v>30</v>
@@ -7798,7 +7913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>2016</v>
       </c>
@@ -7833,77 +7948,77 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A197">
-        <v>2117</v>
+        <v>2101</v>
       </c>
       <c r="B197" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C197" t="s">
         <v>27</v>
       </c>
       <c r="D197" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E197" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F197" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G197">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H197">
-        <v>164.37</v>
+        <v>6.51</v>
       </c>
       <c r="I197">
-        <v>5424.24</v>
+        <v>149.63</v>
       </c>
       <c r="J197" t="s">
         <v>30</v>
       </c>
       <c r="K197" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A198">
-        <v>2240</v>
+        <v>2105</v>
       </c>
       <c r="B198" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C198" t="s">
         <v>27</v>
       </c>
       <c r="D198" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E198" t="s">
         <v>14</v>
       </c>
       <c r="F198" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="G198">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H198">
-        <v>178.62</v>
+        <v>72.819999999999993</v>
       </c>
       <c r="I198">
-        <v>5179.9399999999996</v>
+        <v>145.63999999999999</v>
       </c>
       <c r="J198" t="s">
         <v>30</v>
       </c>
       <c r="K198" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>2127</v>
       </c>
@@ -7938,53 +8053,53 @@
         <v>31</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A200">
-        <v>2110</v>
+        <v>2278</v>
       </c>
       <c r="B200" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C200" t="s">
         <v>12</v>
       </c>
       <c r="D200" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E200" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F200" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G200">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="H200">
-        <v>25.48</v>
+        <v>4.24</v>
       </c>
       <c r="I200">
-        <v>1885.57</v>
+        <v>135.71</v>
       </c>
       <c r="J200" t="s">
         <v>30</v>
       </c>
       <c r="K200" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A201">
-        <v>2047</v>
+        <v>2015</v>
       </c>
       <c r="B201" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C201" t="s">
         <v>32</v>
       </c>
       <c r="D201" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E201" t="s">
         <v>44</v>
@@ -7993,22 +8108,22 @@
         <v>48</v>
       </c>
       <c r="G201">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="H201">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="I201">
-        <v>255.19</v>
+        <v>38.590000000000003</v>
       </c>
       <c r="J201" t="s">
         <v>30</v>
       </c>
       <c r="K201" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>2091</v>
       </c>
@@ -8043,190 +8158,190 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A203">
-        <v>2092</v>
+        <v>2230</v>
       </c>
       <c r="B203" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C203" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D203" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E203" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F203" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G203">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="H203">
-        <v>19.3</v>
+        <v>3.61</v>
       </c>
       <c r="I203">
-        <v>1427.94</v>
+        <v>3.61</v>
       </c>
       <c r="J203" t="s">
         <v>30</v>
       </c>
       <c r="K203" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A204">
-        <v>2066</v>
+        <v>2269</v>
       </c>
       <c r="B204" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C204" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D204" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E204" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F204" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G204">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H204">
-        <v>3.79</v>
+        <v>744.46</v>
       </c>
       <c r="I204">
-        <v>242.75</v>
+        <v>50623.56</v>
       </c>
       <c r="J204" t="s">
         <v>30</v>
       </c>
       <c r="K204" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A205">
-        <v>2063</v>
+        <v>2185</v>
       </c>
       <c r="B205" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C205" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D205" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E205" t="s">
+        <v>14</v>
+      </c>
+      <c r="F205" t="s">
+        <v>68</v>
+      </c>
+      <c r="G205">
         <v>44</v>
       </c>
-      <c r="F205" t="s">
-        <v>65</v>
-      </c>
-      <c r="G205">
-        <v>75</v>
-      </c>
       <c r="H205">
-        <v>3.12</v>
+        <v>873.88</v>
       </c>
       <c r="I205">
-        <v>234.36</v>
+        <v>38450.699999999997</v>
       </c>
       <c r="J205" t="s">
         <v>30</v>
       </c>
       <c r="K205" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A206">
-        <v>2214</v>
+        <v>2138</v>
       </c>
       <c r="B206" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="C206" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D206" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E206" t="s">
         <v>14</v>
       </c>
       <c r="F206" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G206">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="H206">
-        <v>21.93</v>
+        <v>295.58</v>
       </c>
       <c r="I206">
-        <v>219.3</v>
+        <v>22463.9</v>
       </c>
       <c r="J206" t="s">
         <v>30</v>
       </c>
       <c r="K206" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A207">
-        <v>2267</v>
+        <v>2271</v>
       </c>
       <c r="B207" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C207" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D207" t="s">
         <v>20</v>
       </c>
       <c r="E207" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="G207">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="H207">
-        <v>288.69</v>
+        <v>315.66000000000003</v>
       </c>
       <c r="I207">
-        <v>577.39</v>
+        <v>20202.25</v>
       </c>
       <c r="J207" t="s">
         <v>30</v>
       </c>
       <c r="K207" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A208">
-        <v>2269</v>
+        <v>2022</v>
       </c>
       <c r="B208" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D208" t="s">
         <v>20</v>
@@ -8235,25 +8350,25 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="G208">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H208">
-        <v>744.46</v>
+        <v>327.58999999999997</v>
       </c>
       <c r="I208">
-        <v>50623.56</v>
+        <v>14086.19</v>
       </c>
       <c r="J208" t="s">
         <v>30</v>
       </c>
       <c r="K208" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>2248</v>
       </c>
@@ -8288,15 +8403,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A210">
-        <v>2271</v>
+        <v>2044</v>
       </c>
       <c r="B210" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="C210" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D210" t="s">
         <v>20</v>
@@ -8308,22 +8423,22 @@
         <v>62</v>
       </c>
       <c r="G210">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="H210">
-        <v>315.66000000000003</v>
+        <v>367.57</v>
       </c>
       <c r="I210">
-        <v>20202.25</v>
+        <v>10659.45</v>
       </c>
       <c r="J210" t="s">
         <v>30</v>
       </c>
       <c r="K210" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>2002</v>
       </c>
@@ -8358,12 +8473,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A212">
-        <v>2022</v>
+        <v>2300</v>
       </c>
       <c r="B212" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C212" t="s">
         <v>27</v>
@@ -8375,30 +8490,30 @@
         <v>21</v>
       </c>
       <c r="F212" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G212">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H212">
-        <v>327.58999999999997</v>
+        <v>120</v>
       </c>
       <c r="I212">
-        <v>14086.19</v>
+        <v>8399.98</v>
       </c>
       <c r="J212" t="s">
         <v>30</v>
       </c>
       <c r="K212" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A213">
-        <v>2044</v>
+        <v>2225</v>
       </c>
       <c r="B213" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="C213" t="s">
         <v>12</v>
@@ -8410,30 +8525,30 @@
         <v>21</v>
       </c>
       <c r="F213" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G213">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="H213">
-        <v>367.57</v>
+        <v>110.14</v>
       </c>
       <c r="I213">
-        <v>10659.45</v>
+        <v>7929.85</v>
       </c>
       <c r="J213" t="s">
         <v>30</v>
       </c>
       <c r="K213" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A214">
-        <v>2300</v>
+        <v>2270</v>
       </c>
       <c r="B214" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C214" t="s">
         <v>27</v>
@@ -8445,16 +8560,16 @@
         <v>21</v>
       </c>
       <c r="F214" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="G214">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="H214">
-        <v>120</v>
+        <v>826.36</v>
       </c>
       <c r="I214">
-        <v>8399.98</v>
+        <v>6610.89</v>
       </c>
       <c r="J214" t="s">
         <v>30</v>
@@ -8463,42 +8578,42 @@
         <v>23</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A215">
-        <v>2225</v>
+        <v>2117</v>
       </c>
       <c r="B215" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C215" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D215" t="s">
         <v>20</v>
       </c>
       <c r="E215" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F215" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="G215">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="H215">
-        <v>110.14</v>
+        <v>164.37</v>
       </c>
       <c r="I215">
-        <v>7929.85</v>
+        <v>5424.24</v>
       </c>
       <c r="J215" t="s">
         <v>30</v>
       </c>
       <c r="K215" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>2024</v>
       </c>
@@ -8533,12 +8648,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A217">
-        <v>2270</v>
+        <v>2240</v>
       </c>
       <c r="B217" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C217" t="s">
         <v>27</v>
@@ -8547,19 +8662,19 @@
         <v>20</v>
       </c>
       <c r="E217" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F217" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G217">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H217">
-        <v>826.36</v>
+        <v>178.62</v>
       </c>
       <c r="I217">
-        <v>6610.89</v>
+        <v>5179.9399999999996</v>
       </c>
       <c r="J217" t="s">
         <v>30</v>
@@ -8568,7 +8683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>2020</v>
       </c>
@@ -8603,7 +8718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>2009</v>
       </c>
@@ -8638,7 +8753,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>2238</v>
       </c>
@@ -8673,7 +8788,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>2174</v>
       </c>
@@ -8743,7 +8858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>2055</v>
       </c>
@@ -8778,12 +8893,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A224">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="B224" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C224" t="s">
         <v>12</v>
@@ -8792,28 +8907,28 @@
         <v>20</v>
       </c>
       <c r="E224" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F224" t="s">
+        <v>52</v>
+      </c>
+      <c r="G224">
         <v>74</v>
       </c>
-      <c r="G224">
-        <v>64</v>
-      </c>
       <c r="H224">
-        <v>6.42</v>
+        <v>25.48</v>
       </c>
       <c r="I224">
-        <v>411</v>
+        <v>1885.57</v>
       </c>
       <c r="J224" t="s">
         <v>30</v>
       </c>
       <c r="K224" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>2048</v>
       </c>
@@ -8883,53 +8998,53 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A227">
-        <v>2026</v>
+        <v>2154</v>
       </c>
       <c r="B227" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C227" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D227" t="s">
         <v>20</v>
       </c>
       <c r="E227" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F227" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G227">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H227">
-        <v>3.03</v>
+        <v>27.2</v>
       </c>
       <c r="I227">
-        <v>242.8</v>
+        <v>1605.07</v>
       </c>
       <c r="J227" t="s">
         <v>30</v>
       </c>
       <c r="K227" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A228">
-        <v>2056</v>
+        <v>2092</v>
       </c>
       <c r="B228" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C228" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E228" t="s">
         <v>14</v>
@@ -8938,22 +9053,22 @@
         <v>29</v>
       </c>
       <c r="G228">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="H228">
-        <v>18.12</v>
+        <v>19.3</v>
       </c>
       <c r="I228">
-        <v>144.97999999999999</v>
+        <v>1427.94</v>
       </c>
       <c r="J228" t="s">
         <v>30</v>
       </c>
       <c r="K228" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>2052</v>
       </c>
@@ -8990,45 +9105,45 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A230">
-        <v>2012</v>
+        <v>2267</v>
       </c>
       <c r="B230" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C230" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D230" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E230" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F230" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G230">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="H230">
-        <v>1.55</v>
+        <v>288.69</v>
       </c>
       <c r="I230">
-        <v>113.04</v>
+        <v>577.39</v>
       </c>
       <c r="J230" t="s">
         <v>30</v>
       </c>
       <c r="K230" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A231">
-        <v>2177</v>
+        <v>2086</v>
       </c>
       <c r="B231" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C231" t="s">
         <v>12</v>
@@ -9040,16 +9155,16 @@
         <v>44</v>
       </c>
       <c r="F231" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G231">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H231">
-        <v>3.13</v>
+        <v>6.42</v>
       </c>
       <c r="I231">
-        <v>100.03</v>
+        <v>411</v>
       </c>
       <c r="J231" t="s">
         <v>30</v>
@@ -9058,7 +9173,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>2148</v>
       </c>
@@ -9093,15 +9208,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A233">
-        <v>2226</v>
+        <v>2163</v>
       </c>
       <c r="B233" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C233" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D233" t="s">
         <v>20</v>
@@ -9110,33 +9225,33 @@
         <v>44</v>
       </c>
       <c r="F233" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G233">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H233">
-        <v>1.57</v>
+        <v>5.77</v>
       </c>
       <c r="I233">
-        <v>61.23</v>
+        <v>410.01</v>
       </c>
       <c r="J233" t="s">
         <v>30</v>
       </c>
       <c r="K233" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A234">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="B234" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C234" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D234" t="s">
         <v>20</v>
@@ -9145,16 +9260,16 @@
         <v>44</v>
       </c>
       <c r="F234" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G234">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H234">
-        <v>1.48</v>
+        <v>3.03</v>
       </c>
       <c r="I234">
-        <v>54.6</v>
+        <v>242.8</v>
       </c>
       <c r="J234" t="s">
         <v>30</v>
@@ -9163,7 +9278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>2035</v>
       </c>
@@ -9198,7 +9313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>2062</v>
       </c>
@@ -9233,7 +9348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>2292</v>
       </c>
@@ -9268,7 +9383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>2023</v>
       </c>
@@ -9303,7 +9418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>2296</v>
       </c>
@@ -9340,31 +9455,31 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A240">
-        <v>2128</v>
+        <v>2177</v>
       </c>
       <c r="B240" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="C240" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D240" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E240" t="s">
         <v>44</v>
       </c>
       <c r="F240" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G240">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="H240">
-        <v>1.52</v>
+        <v>3.13</v>
       </c>
       <c r="I240">
-        <v>107.92</v>
+        <v>100.03</v>
       </c>
       <c r="J240" t="s">
         <v>30</v>
@@ -9373,42 +9488,42 @@
         <v>23</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A241">
-        <v>2184</v>
+        <v>2226</v>
       </c>
       <c r="B241" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="C241" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D241" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E241" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F241" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G241">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H241">
-        <v>69.89</v>
+        <v>1.57</v>
       </c>
       <c r="I241">
-        <v>1397.86</v>
+        <v>61.23</v>
       </c>
       <c r="J241" t="s">
         <v>30</v>
       </c>
       <c r="K241" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>2059</v>
       </c>
@@ -9443,39 +9558,39 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A243">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="B243" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="C243" t="s">
         <v>27</v>
       </c>
       <c r="D243" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E243" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F243" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G243">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H243">
-        <v>20.11</v>
+        <v>1.48</v>
       </c>
       <c r="I243">
-        <v>1186.57</v>
+        <v>54.6</v>
       </c>
       <c r="J243" t="s">
         <v>30</v>
       </c>
       <c r="K243" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.45">
@@ -9515,48 +9630,48 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A245">
-        <v>2245</v>
+        <v>2182</v>
       </c>
       <c r="B245" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="C245" t="s">
+        <v>27</v>
+      </c>
+      <c r="D245" t="s">
+        <v>28</v>
+      </c>
+      <c r="E245" t="s">
+        <v>21</v>
+      </c>
+      <c r="F245" t="s">
+        <v>22</v>
+      </c>
+      <c r="G245">
+        <v>54</v>
+      </c>
+      <c r="H245">
+        <v>213.89</v>
+      </c>
+      <c r="I245">
+        <v>11549.92</v>
+      </c>
+      <c r="J245" t="s">
+        <v>30</v>
+      </c>
+      <c r="K245" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A246">
+        <v>2235</v>
+      </c>
+      <c r="B246" t="s">
+        <v>61</v>
+      </c>
+      <c r="C246" t="s">
         <v>32</v>
-      </c>
-      <c r="D245" t="s">
-        <v>13</v>
-      </c>
-      <c r="E245" t="s">
-        <v>44</v>
-      </c>
-      <c r="F245" t="s">
-        <v>65</v>
-      </c>
-      <c r="G245">
-        <v>29</v>
-      </c>
-      <c r="H245">
-        <v>2.98</v>
-      </c>
-      <c r="I245">
-        <v>86.44</v>
-      </c>
-      <c r="J245" t="s">
-        <v>30</v>
-      </c>
-      <c r="K245" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A246">
-        <v>2200</v>
-      </c>
-      <c r="B246" t="s">
-        <v>60</v>
-      </c>
-      <c r="C246" t="s">
-        <v>12</v>
       </c>
       <c r="D246" t="s">
         <v>28</v>
@@ -9565,25 +9680,25 @@
         <v>14</v>
       </c>
       <c r="F246" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G246">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="H246">
-        <v>55.25</v>
+        <v>188.4</v>
       </c>
       <c r="I246">
-        <v>165.75</v>
+        <v>10361.99</v>
       </c>
       <c r="J246" t="s">
         <v>30</v>
       </c>
       <c r="K246" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>2096</v>
       </c>
@@ -9618,7 +9733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>2283</v>
       </c>
@@ -9653,12 +9768,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A249">
-        <v>2182</v>
+        <v>2102</v>
       </c>
       <c r="B249" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="C249" t="s">
         <v>27</v>
@@ -9670,25 +9785,25 @@
         <v>21</v>
       </c>
       <c r="F249" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G249">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H249">
-        <v>213.89</v>
+        <v>125.5</v>
       </c>
       <c r="I249">
-        <v>11549.92</v>
+        <v>5521.98</v>
       </c>
       <c r="J249" t="s">
         <v>30</v>
       </c>
       <c r="K249" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>2079</v>
       </c>
@@ -9723,7 +9838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>2169</v>
       </c>
@@ -9758,39 +9873,39 @@
         <v>23</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A252">
-        <v>2102</v>
+        <v>2184</v>
       </c>
       <c r="B252" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C252" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D252" t="s">
         <v>28</v>
       </c>
       <c r="E252" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F252" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G252">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H252">
-        <v>125.5</v>
+        <v>69.89</v>
       </c>
       <c r="I252">
-        <v>5521.98</v>
+        <v>1397.86</v>
       </c>
       <c r="J252" t="s">
         <v>30</v>
       </c>
       <c r="K252" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.45">
@@ -9830,31 +9945,31 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A254">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="B254" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C254" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D254" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E254" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F254" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G254">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="H254">
-        <v>3.86</v>
+        <v>20.11</v>
       </c>
       <c r="I254">
-        <v>38.590000000000003</v>
+        <v>1186.57</v>
       </c>
       <c r="J254" t="s">
         <v>30</v>
@@ -9863,7 +9978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>2074</v>
       </c>
@@ -9898,7 +10013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>2162</v>
       </c>
@@ -9933,7 +10048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>2139</v>
       </c>
@@ -9968,7 +10083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>2272</v>
       </c>
@@ -10003,33 +10118,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A259">
-        <v>2295</v>
+        <v>2214</v>
       </c>
       <c r="B259" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C259" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D259" t="s">
         <v>28</v>
       </c>
       <c r="E259" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F259" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G259">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H259">
-        <v>3.11</v>
+        <v>21.93</v>
       </c>
       <c r="I259">
-        <v>124.25</v>
+        <v>219.3</v>
       </c>
       <c r="J259" t="s">
         <v>30</v>
@@ -10038,7 +10153,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>2140</v>
       </c>
@@ -10073,7 +10188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>2158</v>
       </c>
@@ -10108,50 +10223,50 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A262">
-        <v>2215</v>
+        <v>2200</v>
       </c>
       <c r="B262" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C262" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D262" t="s">
         <v>28</v>
       </c>
       <c r="E262" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F262" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G262">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H262">
-        <v>2.91</v>
+        <v>55.25</v>
       </c>
       <c r="I262">
-        <v>104.83</v>
+        <v>165.75</v>
       </c>
       <c r="J262" t="s">
         <v>30</v>
       </c>
       <c r="K262" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A263">
-        <v>2129</v>
+        <v>2295</v>
       </c>
       <c r="B263" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C263" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D263" t="s">
         <v>28</v>
@@ -10160,36 +10275,36 @@
         <v>44</v>
       </c>
       <c r="F263" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G263">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H263">
-        <v>1.5</v>
+        <v>3.11</v>
       </c>
       <c r="I263">
-        <v>76.72</v>
+        <v>124.25</v>
       </c>
       <c r="J263" t="s">
         <v>30</v>
       </c>
       <c r="K263" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A264">
-        <v>2025</v>
+        <v>2215</v>
       </c>
       <c r="B264" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="C264" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D264" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E264" t="s">
         <v>44</v>
@@ -10198,30 +10313,30 @@
         <v>65</v>
       </c>
       <c r="G264">
+        <v>36</v>
+      </c>
+      <c r="H264">
+        <v>2.91</v>
+      </c>
+      <c r="I264">
+        <v>104.83</v>
+      </c>
+      <c r="J264" t="s">
+        <v>30</v>
+      </c>
+      <c r="K264" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A265">
+        <v>2129</v>
+      </c>
+      <c r="B265" t="s">
+        <v>104</v>
+      </c>
+      <c r="C265" t="s">
         <v>12</v>
-      </c>
-      <c r="H264">
-        <v>3.15</v>
-      </c>
-      <c r="I264">
-        <v>37.76</v>
-      </c>
-      <c r="J264" t="s">
-        <v>30</v>
-      </c>
-      <c r="K264" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A265">
-        <v>2119</v>
-      </c>
-      <c r="B265" t="s">
-        <v>115</v>
-      </c>
-      <c r="C265" t="s">
-        <v>19</v>
       </c>
       <c r="D265" t="s">
         <v>28</v>
@@ -10233,13 +10348,13 @@
         <v>50</v>
       </c>
       <c r="G265">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H265">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="I265">
-        <v>5.72</v>
+        <v>76.72</v>
       </c>
       <c r="J265" t="s">
         <v>30</v>
@@ -10248,50 +10363,50 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A266">
+        <v>2119</v>
+      </c>
+      <c r="B266" t="s">
+        <v>115</v>
+      </c>
+      <c r="C266" t="s">
+        <v>19</v>
+      </c>
+      <c r="D266" t="s">
+        <v>28</v>
+      </c>
+      <c r="E266" t="s">
+        <v>44</v>
+      </c>
+      <c r="F266" t="s">
+        <v>50</v>
+      </c>
+      <c r="G266">
+        <v>4</v>
+      </c>
+      <c r="H266">
+        <v>1.43</v>
+      </c>
+      <c r="I266">
+        <v>5.72</v>
+      </c>
+      <c r="J266" t="s">
+        <v>30</v>
+      </c>
+      <c r="K266" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A267">
         <v>2290</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B267" t="s">
         <v>70</v>
       </c>
-      <c r="C266" t="s">
+      <c r="C267" t="s">
         <v>12</v>
-      </c>
-      <c r="D266" t="s">
-        <v>58</v>
-      </c>
-      <c r="E266" t="s">
-        <v>14</v>
-      </c>
-      <c r="F266" t="s">
-        <v>68</v>
-      </c>
-      <c r="G266">
-        <v>76</v>
-      </c>
-      <c r="H266">
-        <v>837.45</v>
-      </c>
-      <c r="I266">
-        <v>63646.29</v>
-      </c>
-      <c r="J266" t="s">
-        <v>30</v>
-      </c>
-      <c r="K266" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A267">
-        <v>2287</v>
-      </c>
-      <c r="B267" t="s">
-        <v>54</v>
-      </c>
-      <c r="C267" t="s">
-        <v>27</v>
       </c>
       <c r="D267" t="s">
         <v>58</v>
@@ -10303,22 +10418,22 @@
         <v>68</v>
       </c>
       <c r="G267">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="H267">
-        <v>898.37</v>
+        <v>837.45</v>
       </c>
       <c r="I267">
-        <v>46715.48</v>
+        <v>63646.29</v>
       </c>
       <c r="J267" t="s">
         <v>30</v>
       </c>
       <c r="K267" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>2150</v>
       </c>
@@ -10353,15 +10468,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A269">
-        <v>2178</v>
+        <v>2287</v>
       </c>
       <c r="B269" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="C269" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D269" t="s">
         <v>58</v>
@@ -10370,65 +10485,65 @@
         <v>14</v>
       </c>
       <c r="F269" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G269">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="H269">
-        <v>186.54</v>
+        <v>898.37</v>
       </c>
       <c r="I269">
-        <v>13804.27</v>
+        <v>46715.48</v>
       </c>
       <c r="J269" t="s">
         <v>30</v>
       </c>
       <c r="K269" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A270">
-        <v>2183</v>
+        <v>2266</v>
       </c>
       <c r="B270" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C270" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D270" t="s">
         <v>58</v>
       </c>
       <c r="E270" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F270" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="G270">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H270">
-        <v>75.900000000000006</v>
+        <v>842.21</v>
       </c>
       <c r="I270">
-        <v>3718.99</v>
+        <v>26950.61</v>
       </c>
       <c r="J270" t="s">
         <v>30</v>
       </c>
       <c r="K270" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A271">
-        <v>2189</v>
+        <v>2178</v>
       </c>
       <c r="B271" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C271" t="s">
         <v>12</v>
@@ -10440,16 +10555,16 @@
         <v>14</v>
       </c>
       <c r="F271" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G271">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="H271">
-        <v>906.8</v>
+        <v>186.54</v>
       </c>
       <c r="I271">
-        <v>3627.21</v>
+        <v>13804.27</v>
       </c>
       <c r="J271" t="s">
         <v>30</v>
@@ -10458,7 +10573,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>2211</v>
       </c>
@@ -10493,42 +10608,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A273">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B273" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C273" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D273" t="s">
         <v>58</v>
       </c>
       <c r="E273" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F273" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G273">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H273">
-        <v>20.88</v>
+        <v>191.9</v>
       </c>
       <c r="I273">
-        <v>1085.82</v>
+        <v>12665.24</v>
       </c>
       <c r="J273" t="s">
         <v>30</v>
       </c>
       <c r="K273" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>2237</v>
       </c>
@@ -10563,7 +10678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>2212</v>
       </c>
@@ -10598,50 +10713,50 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A276">
-        <v>2085</v>
+        <v>2098</v>
       </c>
       <c r="B276" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C276" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D276" t="s">
         <v>58</v>
       </c>
       <c r="E276" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F276" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G276">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="H276">
-        <v>20.91</v>
+        <v>180.41</v>
       </c>
       <c r="I276">
-        <v>250.86</v>
+        <v>12628.41</v>
       </c>
       <c r="J276" t="s">
         <v>30</v>
       </c>
       <c r="K276" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A277">
-        <v>2266</v>
+        <v>2232</v>
       </c>
       <c r="B277" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="C277" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D277" t="s">
         <v>58</v>
@@ -10650,16 +10765,16 @@
         <v>21</v>
       </c>
       <c r="F277" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="G277">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H277">
-        <v>842.21</v>
+        <v>352.03</v>
       </c>
       <c r="I277">
-        <v>26950.61</v>
+        <v>4576.33</v>
       </c>
       <c r="J277" t="s">
         <v>30</v>
@@ -10668,7 +10783,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>2280</v>
       </c>
@@ -10703,7 +10818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>2151</v>
       </c>
@@ -10738,68 +10853,68 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A280">
-        <v>2028</v>
+        <v>2183</v>
       </c>
       <c r="B280" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C280" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D280" t="s">
         <v>58</v>
       </c>
       <c r="E280" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F280" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G280">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H280">
-        <v>191.9</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="I280">
-        <v>12665.24</v>
+        <v>3718.99</v>
       </c>
       <c r="J280" t="s">
         <v>30</v>
       </c>
       <c r="K280" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A281">
-        <v>2098</v>
+        <v>2189</v>
       </c>
       <c r="B281" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C281" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D281" t="s">
         <v>58</v>
       </c>
       <c r="E281" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F281" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="G281">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="H281">
-        <v>180.41</v>
+        <v>906.8</v>
       </c>
       <c r="I281">
-        <v>12628.41</v>
+        <v>3627.21</v>
       </c>
       <c r="J281" t="s">
         <v>30</v>
@@ -10808,7 +10923,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>2112</v>
       </c>
@@ -10843,7 +10958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>2103</v>
       </c>
@@ -10878,7 +10993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>2107</v>
       </c>
@@ -10913,7 +11028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>2123</v>
       </c>
@@ -10948,7 +11063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>2173</v>
       </c>
@@ -10985,66 +11100,66 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A287">
-        <v>2136</v>
+        <v>2033</v>
       </c>
       <c r="B287" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="C287" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D287" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E287" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F287" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="G287">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H287">
-        <v>1.58</v>
+        <v>20.88</v>
       </c>
       <c r="I287">
-        <v>33.159999999999997</v>
+        <v>1085.82</v>
       </c>
       <c r="J287" t="s">
         <v>30</v>
       </c>
       <c r="K287" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A288">
-        <v>2242</v>
+        <v>2085</v>
       </c>
       <c r="B288" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C288" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D288" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E288" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F288" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G288">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H288">
-        <v>3.93</v>
+        <v>20.91</v>
       </c>
       <c r="I288">
-        <v>31.45</v>
+        <v>250.86</v>
       </c>
       <c r="J288" t="s">
         <v>30</v>
@@ -11123,7 +11238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>2288</v>
       </c>
@@ -11158,7 +11273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>2273</v>
       </c>
@@ -11193,7 +11308,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>2256</v>
       </c>
@@ -11228,7 +11343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>2116</v>
       </c>
@@ -11263,7 +11378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>2186</v>
       </c>
@@ -11298,7 +11413,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>2153</v>
       </c>
@@ -11333,7 +11448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>2157</v>
       </c>
@@ -11368,7 +11483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>2106</v>
       </c>
@@ -11403,7 +11518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>2070</v>
       </c>
@@ -11473,7 +11588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>2130</v>
       </c>
@@ -11508,129 +11623,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="D303" t="s">
-        <v>14</v>
-      </c>
-      <c r="E303">
-        <f>COUNTIF(E2:E97, "Electronics")</f>
-        <v>36</v>
-      </c>
-      <c r="F303">
-        <f>COUNTIF(E4:E89, "Electronics")</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="D304" t="s">
-        <v>162</v>
-      </c>
-      <c r="E304">
-        <v>100</v>
-      </c>
-      <c r="F304">
-        <f>COUNTIF(E92:E178, "Furniture")</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="305" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D305" t="s">
-        <v>44</v>
-      </c>
-      <c r="E305">
-        <f>COUNTIF(E198:E301, "Office Supplies")</f>
-        <v>46</v>
-      </c>
-      <c r="F305">
-        <f>COUNTIF(E179:E301, "Office Supplies")</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="307" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D307" t="s">
-        <v>13</v>
-      </c>
-      <c r="E307">
-        <f>COUNTIF(D2:D46, "Brown")</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="308" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D308" t="s">
-        <v>36</v>
-      </c>
-      <c r="E308">
-        <f>COUNTIF(D47:D81, "Chen")</f>
-        <v>27</v>
-      </c>
-      <c r="G308">
-        <f>COUNTIF(C:C, "Electronics")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D309" t="s">
-        <v>33</v>
-      </c>
-      <c r="E309">
-        <f>COUNTIF(D82:D122, "Garcia")</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="310" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D310" t="s">
-        <v>47</v>
-      </c>
-      <c r="E310">
-        <f>COUNTIF(D123:D154, "Johnson")</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="311" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D311" t="s">
-        <v>40</v>
-      </c>
-      <c r="E311">
-        <f>COUNTIF(D155:D192, "Kim")</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="312" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D312" t="s">
-        <v>20</v>
-      </c>
-      <c r="E312">
-        <f>COUNTIF(D193:D235, "Lopez")</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="313" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D313" t="s">
-        <v>28</v>
-      </c>
-      <c r="E313">
-        <f>COUNTIF(D236:D265, "Patel")</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="314" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D314" t="s">
-        <v>58</v>
-      </c>
-      <c r="E314">
-        <f>COUNTIF(D266:D301, "Singh" )</f>
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:K301" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="East"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K300">
-      <sortCondition descending="1" ref="I1:I301"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K301">
+      <sortCondition ref="D1:D301"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K301">
@@ -11641,6 +11637,451 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408FFCEE-6282-4CF3-8786-528248477B6D}">
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
+    <col min="2" max="2" width="20.06640625" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" customWidth="1"/>
+    <col min="5" max="5" width="21.19921875" customWidth="1"/>
+    <col min="6" max="6" width="18.86328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIFS(Sales_Data!E1:E300, "Electronics", Sales_Data!C1:C300, "East")</f>
+        <v>33</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
+        <f>COUNTIFS(Sales_Data!E2:E302, "Furniture", Sales_Data!C2:C302, "East")</f>
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <f>COUNTIFS(Sales_Data!E2:E301, "Office Supplies", Sales_Data!C2:C301, "East")</f>
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Brown", Sales_Data!C2:C301, "East")</f>
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Chen", Sales_Data!C2:C301, "East")</f>
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Garcia", Sales_Data!C2:C301, "East")</f>
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Johnson", Sales_Data!C2:C301, "East")</f>
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Kim", Sales_Data!C2:C301, "East")</f>
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Lopez", Sales_Data!C2:C301, "East")</f>
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Patel", Sales_Data!C2:C301, "East")</f>
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(Sales_Data!D2:D301, "Singh", Sales_Data!C2:C301, "East")</f>
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="4">
+        <f>COUNTIFS(Sales_Data!E:E, "Electronics", Sales_Data!J:J, "Business")</f>
+        <v>50</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18">
+        <f>COUNTIFS(Sales_Data!E:E, "Furniture", Sales_Data!J:J, "Business")</f>
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <f>COUNTIFS(Sales_Data!E:E, "Office Supplies", Sales_Data!J:J, "Business")</f>
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <f>COUNTIFS(Sales_Data!D:D, "Brown", Sales_Data!J:J, "Business")</f>
+        <v>25</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <f>COUNTIFS(Sales_Data!D:D, "Chen", Sales_Data!J:J, "Business")</f>
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <f>COUNTIFS(Sales_Data!D:D, "Garcia", Sales_Data!J:J, "Business")</f>
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24">
+        <f>COUNTIFS(Sales_Data!D:D, "Johnson", Sales_Data!J:J, "Business")</f>
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25">
+        <f>COUNTIFS(Sales_Data!D:D, "Kim", Sales_Data!J:J, "Business")</f>
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <f>COUNTIFS(Sales_Data!D:D, "Lopez", Sales_Data!J:J, "Business")</f>
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <f>COUNTIFS(Sales_Data!D:D, "Patel", Sales_Data!J:J, "Business")</f>
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28">
+        <f>COUNTIFS(Sales_Data!D:D, "Singh", Sales_Data!J:J, "Business")</f>
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="1"/>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C3:C4 C6:C10" calculatedColumn="1"/>
+  </ignoredErrors>
+  <tableParts count="5">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B20F9A-CCAA-43BD-8D19-AEE7F2610A5B}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -11707,8 +12148,8 @@
       <c r="A5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>20</v>
+      <c r="B5" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>157</v>
@@ -11744,7 +12185,7 @@
     </row>
     <row r="9" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>44</v>
@@ -11758,7 +12199,7 @@
       <c r="A10" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>63646.29</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -11769,6 +12210,9 @@
     <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>143</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>161</v>

--- a/week-01/techsupply_dataset1.xlsx
+++ b/week-01/techsupply_dataset1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED436E4C-B857-4F81-B4A4-BD3F9A95F794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15329B4C-AC11-4CB2-A025-77D1A950C93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="16485" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
@@ -1075,6 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K301"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1193,7 +1194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2208</v>
       </c>
@@ -1263,7 +1264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2134</v>
       </c>
@@ -1298,7 +1299,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2077</v>
       </c>
@@ -1368,7 +1369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2229</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2001</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2109</v>
       </c>
@@ -1473,7 +1474,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2003</v>
       </c>
@@ -1543,7 +1544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>2202</v>
       </c>
@@ -1613,7 +1614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2032</v>
       </c>
@@ -1753,7 +1754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>2247</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>2076</v>
       </c>
@@ -1823,7 +1824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2073</v>
       </c>
@@ -1858,7 +1859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>2293</v>
       </c>
@@ -1893,7 +1894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>2113</v>
       </c>
@@ -1928,7 +1929,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>2097</v>
       </c>
@@ -1963,7 +1964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>2275</v>
       </c>
@@ -1998,7 +1999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2286</v>
       </c>
@@ -2068,7 +2069,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2294</v>
       </c>
@@ -2103,7 +2104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>2031</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2088</v>
       </c>
@@ -2173,7 +2174,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>2159</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>2219</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>2206</v>
       </c>
@@ -2313,7 +2314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2010</v>
       </c>
@@ -2348,7 +2349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>2121</v>
       </c>
@@ -2383,7 +2384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>2069</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>2095</v>
       </c>
@@ -2453,7 +2454,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>2222</v>
       </c>
@@ -2558,7 +2559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>2037</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>2161</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>2115</v>
       </c>
@@ -2663,7 +2664,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>2155</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>2017</v>
       </c>
@@ -2873,7 +2874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>2080</v>
       </c>
@@ -2908,7 +2909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>2006</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>2036</v>
       </c>
@@ -2978,7 +2979,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>2014</v>
       </c>
@@ -3013,7 +3014,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>2207</v>
       </c>
@@ -3118,7 +3119,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>2175</v>
       </c>
@@ -3188,7 +3189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>2236</v>
       </c>
@@ -3223,7 +3224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>2068</v>
       </c>
@@ -3293,7 +3294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>2078</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>2133</v>
       </c>
@@ -3503,7 +3504,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>2197</v>
       </c>
@@ -3538,7 +3539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>2149</v>
       </c>
@@ -3573,7 +3574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>2264</v>
       </c>
@@ -3643,7 +3644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>2135</v>
       </c>
@@ -3678,7 +3679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>2099</v>
       </c>
@@ -3713,7 +3714,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>2124</v>
       </c>
@@ -3748,7 +3749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>2246</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>2279</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>2274</v>
       </c>
@@ -3888,7 +3889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>2064</v>
       </c>
@@ -3923,7 +3924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>2118</v>
       </c>
@@ -3993,7 +3994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>2227</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>2257</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>2147</v>
       </c>
@@ -4133,7 +4134,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>2261</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>2199</v>
       </c>
@@ -4238,7 +4239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>2122</v>
       </c>
@@ -4308,7 +4309,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>2176</v>
       </c>
@@ -4343,7 +4344,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>2075</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>2282</v>
       </c>
@@ -4448,7 +4449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>2125</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>2042</v>
       </c>
@@ -4553,7 +4554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>2072</v>
       </c>
@@ -4588,7 +4589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>2268</v>
       </c>
@@ -4693,7 +4694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>2217</v>
       </c>
@@ -4728,7 +4729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>2284</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>2234</v>
       </c>
@@ -4868,7 +4869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>2164</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>2276</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>2210</v>
       </c>
@@ -5008,7 +5009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>2262</v>
       </c>
@@ -5043,7 +5044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>2223</v>
       </c>
@@ -5113,7 +5114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>2251</v>
       </c>
@@ -5148,7 +5149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>2233</v>
       </c>
@@ -5218,7 +5219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>2038</v>
       </c>
@@ -5253,7 +5254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>2090</v>
       </c>
@@ -5323,7 +5324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>2204</v>
       </c>
@@ -5393,7 +5394,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>2126</v>
       </c>
@@ -5428,7 +5429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>2299</v>
       </c>
@@ -5533,7 +5534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>2195</v>
       </c>
@@ -5603,7 +5604,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>2187</v>
       </c>
@@ -5638,7 +5639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>2291</v>
       </c>
@@ -5673,7 +5674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>2171</v>
       </c>
@@ -5708,7 +5709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>2265</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>2250</v>
       </c>
@@ -5778,7 +5779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>2094</v>
       </c>
@@ -5813,7 +5814,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>2030</v>
       </c>
@@ -5848,7 +5849,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>2289</v>
       </c>
@@ -5918,7 +5919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>2170</v>
       </c>
@@ -6163,7 +6164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>2252</v>
       </c>
@@ -6198,7 +6199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>2152</v>
       </c>
@@ -6268,7 +6269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>2190</v>
       </c>
@@ -6303,7 +6304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>2084</v>
       </c>
@@ -6338,7 +6339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>2213</v>
       </c>
@@ -6373,7 +6374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>2057</v>
       </c>
@@ -6443,7 +6444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>2179</v>
       </c>
@@ -6478,7 +6479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>2181</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>2191</v>
       </c>
@@ -6583,7 +6584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>2254</v>
       </c>
@@ -6618,7 +6619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>2008</v>
       </c>
@@ -6653,7 +6654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>2218</v>
       </c>
@@ -6688,7 +6689,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>2058</v>
       </c>
@@ -6723,7 +6724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>2013</v>
       </c>
@@ -6758,7 +6759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>2259</v>
       </c>
@@ -6793,7 +6794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>2277</v>
       </c>
@@ -6933,7 +6934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>2255</v>
       </c>
@@ -7003,7 +7004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>2039</v>
       </c>
@@ -7038,7 +7039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>2156</v>
       </c>
@@ -7073,7 +7074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>2145</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>2144</v>
       </c>
@@ -7143,7 +7144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>2196</v>
       </c>
@@ -7178,7 +7179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>2297</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>2049</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>2083</v>
       </c>
@@ -7318,7 +7319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>2258</v>
       </c>
@@ -7423,7 +7424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>2137</v>
       </c>
@@ -7458,7 +7459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>2167</v>
       </c>
@@ -7668,7 +7669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>2114</v>
       </c>
@@ -7703,7 +7704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>2146</v>
       </c>
@@ -7738,7 +7739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>2281</v>
       </c>
@@ -7773,7 +7774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>2221</v>
       </c>
@@ -7808,7 +7809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>2065</v>
       </c>
@@ -7843,7 +7844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>2104</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>2029</v>
       </c>
@@ -7913,7 +7914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>2016</v>
       </c>
@@ -7948,7 +7949,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>2101</v>
       </c>
@@ -7983,7 +7984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>2105</v>
       </c>
@@ -8018,7 +8019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>2127</v>
       </c>
@@ -8053,7 +8054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>2278</v>
       </c>
@@ -8123,7 +8124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>2091</v>
       </c>
@@ -8158,7 +8159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>2230</v>
       </c>
@@ -8193,7 +8194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>2269</v>
       </c>
@@ -8228,7 +8229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>2185</v>
       </c>
@@ -8263,7 +8264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>2138</v>
       </c>
@@ -8298,7 +8299,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>2271</v>
       </c>
@@ -8333,7 +8334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>2022</v>
       </c>
@@ -8368,7 +8369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>2248</v>
       </c>
@@ -8403,7 +8404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>2044</v>
       </c>
@@ -8438,7 +8439,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>2002</v>
       </c>
@@ -8473,7 +8474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>2300</v>
       </c>
@@ -8508,7 +8509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>2225</v>
       </c>
@@ -8543,7 +8544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>2270</v>
       </c>
@@ -8578,7 +8579,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>2117</v>
       </c>
@@ -8613,7 +8614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>2024</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>2240</v>
       </c>
@@ -8683,7 +8684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>2020</v>
       </c>
@@ -8718,7 +8719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>2009</v>
       </c>
@@ -8753,7 +8754,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>2238</v>
       </c>
@@ -8788,7 +8789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>2174</v>
       </c>
@@ -8858,7 +8859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>2055</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>2110</v>
       </c>
@@ -8928,7 +8929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>2048</v>
       </c>
@@ -9033,7 +9034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>2092</v>
       </c>
@@ -9068,7 +9069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>2052</v>
       </c>
@@ -9103,7 +9104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>2267</v>
       </c>
@@ -9138,7 +9139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>2086</v>
       </c>
@@ -9173,7 +9174,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>2148</v>
       </c>
@@ -9243,7 +9244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>2026</v>
       </c>
@@ -9278,7 +9279,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>2035</v>
       </c>
@@ -9313,7 +9314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>2062</v>
       </c>
@@ -9348,7 +9349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>2292</v>
       </c>
@@ -9383,7 +9384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>2023</v>
       </c>
@@ -9418,7 +9419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>2296</v>
       </c>
@@ -9453,7 +9454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>2177</v>
       </c>
@@ -9488,7 +9489,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>2226</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>2059</v>
       </c>
@@ -9558,7 +9559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>2021</v>
       </c>
@@ -9628,7 +9629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>2182</v>
       </c>
@@ -9698,7 +9699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>2096</v>
       </c>
@@ -9733,7 +9734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>2283</v>
       </c>
@@ -9768,7 +9769,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>2102</v>
       </c>
@@ -9803,7 +9804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>2079</v>
       </c>
@@ -9838,7 +9839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>2169</v>
       </c>
@@ -9873,7 +9874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>2184</v>
       </c>
@@ -9943,7 +9944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>2004</v>
       </c>
@@ -9978,7 +9979,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>2074</v>
       </c>
@@ -10013,7 +10014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>2162</v>
       </c>
@@ -10048,7 +10049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>2139</v>
       </c>
@@ -10083,7 +10084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>2272</v>
       </c>
@@ -10153,7 +10154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>2140</v>
       </c>
@@ -10188,7 +10189,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>2158</v>
       </c>
@@ -10223,7 +10224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>2200</v>
       </c>
@@ -10258,7 +10259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>2295</v>
       </c>
@@ -10293,7 +10294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>2215</v>
       </c>
@@ -10328,7 +10329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>2129</v>
       </c>
@@ -10363,7 +10364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>2119</v>
       </c>
@@ -10398,7 +10399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>2290</v>
       </c>
@@ -10433,7 +10434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>2150</v>
       </c>
@@ -10468,7 +10469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>2287</v>
       </c>
@@ -10503,7 +10504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>2266</v>
       </c>
@@ -10538,7 +10539,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>2178</v>
       </c>
@@ -10573,7 +10574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>2211</v>
       </c>
@@ -10608,7 +10609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>2028</v>
       </c>
@@ -10643,7 +10644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>2237</v>
       </c>
@@ -10678,7 +10679,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>2212</v>
       </c>
@@ -10713,7 +10714,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>2098</v>
       </c>
@@ -10783,7 +10784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>2280</v>
       </c>
@@ -10818,7 +10819,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>2151</v>
       </c>
@@ -10853,7 +10854,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>2183</v>
       </c>
@@ -10888,7 +10889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>2189</v>
       </c>
@@ -10923,7 +10924,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>2112</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>2103</v>
       </c>
@@ -10993,7 +10994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>2107</v>
       </c>
@@ -11028,7 +11029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>2123</v>
       </c>
@@ -11063,7 +11064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>2173</v>
       </c>
@@ -11098,7 +11099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>2033</v>
       </c>
@@ -11133,7 +11134,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>2085</v>
       </c>
@@ -11238,7 +11239,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>2288</v>
       </c>
@@ -11273,7 +11274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>2273</v>
       </c>
@@ -11308,7 +11309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>2256</v>
       </c>
@@ -11343,7 +11344,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>2116</v>
       </c>
@@ -11378,7 +11379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>2186</v>
       </c>
@@ -11413,7 +11414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>2153</v>
       </c>
@@ -11448,7 +11449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>2157</v>
       </c>
@@ -11483,7 +11484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>2106</v>
       </c>
@@ -11518,7 +11519,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>2070</v>
       </c>
@@ -11588,7 +11589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>2130</v>
       </c>
@@ -11625,6 +11626,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K301" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="East"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K301">
       <sortCondition ref="D1:D301"/>
     </sortState>

--- a/week-01/techsupply_dataset1.xlsx
+++ b/week-01/techsupply_dataset1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A84DFD-F1A5-40B3-A52E-A645EFC249DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D4F0EF-D25D-4355-90B1-329CB5043A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="473" windowWidth="16485" windowHeight="12060" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="525" windowWidth="16485" windowHeight="12060" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
@@ -732,13 +732,10 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <alignment wrapText="1"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top"/>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -765,7 +762,10 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment vertical="top"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2374,19 +2374,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4720,75 +4708,180 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>The </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>East region appears to be the strongest market leading at $582,615. 11 in total sales across all categories, with the South region following closely behind at $580,102.89</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>The East region appears to be the strongest market leading at $582,615. 11 in total sales across all categories, with the South region following closely behind at $580,102.89</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>Overall, the Furniture category seems to perform the best in terms of total sales across categories. However, offices supplies products ( e.g. filing cabinet, notebooks, printer paper) are ordered more frequently, so there is potential to boost sales there. The company should target office supplies promotions and adjust pricing so that the total sales reflect demand. Since over half of the comapny's cliente are business customers who frequently purchase office supplies, there is high potential for growth in this area.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Overall, the Furniture category seems to perform the best in terms of total sales across categories. However, office supplies products ( e.g. filing cabinets, notebooks, printer paper) are ordered more frequently, so there is potential to boost sales there. The company should target office supplies promotions and adjust pricing so that the total sales reflect demand. Since over half of the company's clients are business customers who frequently purchase office supplies, there is high potential for growth in this area.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>Business customers seem to be more valuable since they make up over 50% of the company's clientele and order more freqently, but retail customera generate slightly higher revenue.Overall, business cusotmers are more consistent and I'd recomment the company focus on strategies or highlight products that can build that same consistency in retail customers. </a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Business customers seem to be more valuable since they make up over 50% of the company's clientele and order more frequently, but retail customers generate slightly higher revenue.Overall, business customers are more consistent and I'd recommend the company focus on strategies or highlight products that can build that same consistency in retail customers.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>Recommendation to Sales Manager:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Prioritize South and East Regions and Assign Top Representatives There</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Brown seems to handle the highest-value transactions but appears most in the West. Assigning representatives like Brown or Lopez to other regions can maximize high-value transactions in both regions and maintain their market.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>1. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>Prioritize South and East Regions and Assign Top Representatives There</a:t>
-          </a:r>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>Brown seems to handle the highest-value transactions but appears most in the West. Assigning representatives like Brown or Lopez to other regions can maximize high-value transactions in both regions and maintain their markert. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>2. </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>Market Office Supplies More Aggresively at Business Customers or Adjust Pricing</a:t>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Market Office Supplies More Aggressively at Business Customers or Adjust Pricing</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>Although office supplies lags in total revenue compared to other categories, it is the most frequently ordered category and with the company's large business cliente, there is a strong opportunity to increase revenue by adjsuting pricing or offering premium porducts to close this gap. </a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Although office supplies lag in total revenue compared to other categories, it is the most frequently ordered category and with the company's large business clients, there is a strong opportunity to increase revenue by adjusting pricing or offering premium products to close this gap. </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -12775,6 +12868,193 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF418852-F8FF-4435-9A05-ADE7B79A99B8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A36:B41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total_Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{215D8339-1A21-448D-900A-7A38E21447F3}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="E29:J39" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="3" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5CB2D040-D6C0-4282-87BB-CC53C8443B76}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="E19:F24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
@@ -12834,7 +13114,7 @@
     <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="10" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -12856,7 +13136,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC8495D6-EAD7-4E6E-9767-6CB1264DFBD0}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="I1:J6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -12907,13 +13187,13 @@
     <dataField name="Average of Total_Sales" fld="8" subtotal="average" baseField="10" baseItem="0"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="10">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="8">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -12922,7 +13202,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -12931,7 +13211,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="5">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -12940,7 +13220,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -12949,7 +13229,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -12965,7 +13245,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E64B4BB9-31FE-4CF9-98C9-98C10494C56E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A43:B62" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -13083,193 +13363,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF418852-F8FF-4435-9A05-ADE7B79A99B8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A36:B41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total_Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{215D8339-1A21-448D-900A-7A38E21447F3}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="E29:J39" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="3" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="11">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5014CB3-2F85-49FE-B634-043A99912F07}" name="PivotTable16" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Customer Type">
   <location ref="A20:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -13313,10 +13406,10 @@
     <dataField name="Count of Customer_Type" fld="0" subtotal="count" baseField="9" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="10">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
   </formats>
@@ -13568,7 +13661,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B26E16DF-4AA3-47A8-A3B5-E25173132F28}" name="Task 1"/>
     <tableColumn id="2" xr3:uid="{BAD8C39B-F492-4029-B8FD-2BF6003A6AFA}" name="East Region Analysis "/>
-    <tableColumn id="3" xr3:uid="{14D5A43A-2AD8-418E-A086-07F6639A83DF}" name="Count" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{14D5A43A-2AD8-418E-A086-07F6639A83DF}" name="Count" dataDxfId="0">
       <calculatedColumnFormula>COUNTIFS(Sales_Data!E1:E300, "Electronics", Sales_Data!C1:C300, "East")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
